--- a/jogos_2026-03-17.xlsx
+++ b/jogos_2026-03-17.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G63" t="n">

--- a/jogos_2026-03-17.xlsx
+++ b/jogos_2026-03-17.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2767,143 +2767,143 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BH12" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="BI12" s="3" t="n">
         <v>46098.625</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,143 +3358,143 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BH15" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="BI15" s="3" t="n">
         <v>46098.625</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3640,10 +3640,10 @@
         <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
         <v>0</v>
@@ -3655,10 +3655,10 @@
         <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3837,10 +3837,10 @@
         <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AS17" t="n">
         <v>0</v>
@@ -3852,10 +3852,10 @@
         <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G63" t="n">

--- a/jogos_2026-03-17.xlsx
+++ b/jogos_2026-03-17.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI63"/>
+  <dimension ref="A1:BI66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2767,143 +2767,143 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="BI12" s="3" t="n">
         <v>46098.625</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,143 +3161,143 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BH14" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="BI14" s="3" t="n">
         <v>46098.625</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3640,10 +3640,10 @@
         <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AS16" t="n">
         <v>0</v>
@@ -3655,10 +3655,10 @@
         <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3837,10 +3837,10 @@
         <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
         <v>0</v>
@@ -3852,10 +3852,10 @@
         <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4285,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="BI19" s="3" t="n">
-        <v>46098.66666666666</v>
+        <v>46098.64583333334</v>
       </c>
     </row>
     <row r="20">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>46098.66666666666</v>
+        <v>46098.64583333334</v>
       </c>
     </row>
     <row r="21">
@@ -4491,12 +4491,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>46098.66666666666</v>
+        <v>46098.64583333334</v>
       </c>
     </row>
     <row r="22">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6264,12 +6264,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6452,7 +6452,7 @@
         <v>0</v>
       </c>
       <c r="BI30" s="3" t="n">
-        <v>46098.6875</v>
+        <v>46098.66666666666</v>
       </c>
     </row>
     <row r="31">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6649,7 +6649,7 @@
         <v>0</v>
       </c>
       <c r="BI31" s="3" t="n">
-        <v>46098.69791666666</v>
+        <v>46098.66666666666</v>
       </c>
     </row>
     <row r="32">
@@ -6658,12 +6658,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6846,7 +6846,7 @@
         <v>0</v>
       </c>
       <c r="BI32" s="3" t="n">
-        <v>46098.69791666666</v>
+        <v>46098.66666666666</v>
       </c>
     </row>
     <row r="33">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7043,7 +7043,7 @@
         <v>0</v>
       </c>
       <c r="BI33" s="3" t="n">
-        <v>46098.69791666666</v>
+        <v>46098.6875</v>
       </c>
     </row>
     <row r="34">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10983,7 +10983,7 @@
         <v>0</v>
       </c>
       <c r="BI53" s="3" t="n">
-        <v>46098.70833333334</v>
+        <v>46098.69791666666</v>
       </c>
     </row>
     <row r="54">
@@ -10992,12 +10992,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11180,7 +11180,7 @@
         <v>0</v>
       </c>
       <c r="BI54" s="3" t="n">
-        <v>46098.70833333334</v>
+        <v>46098.69791666666</v>
       </c>
     </row>
     <row r="55">
@@ -11189,12 +11189,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11377,7 +11377,7 @@
         <v>0</v>
       </c>
       <c r="BI55" s="3" t="n">
-        <v>46098.70833333334</v>
+        <v>46098.69791666666</v>
       </c>
     </row>
     <row r="56">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11583,27 +11583,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11771,7 +11771,7 @@
         <v>0</v>
       </c>
       <c r="BI57" s="3" t="n">
-        <v>46098.77083333334</v>
+        <v>46098.70833333334</v>
       </c>
     </row>
     <row r="58">
@@ -11780,27 +11780,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11968,7 +11968,7 @@
         <v>0</v>
       </c>
       <c r="BI58" s="3" t="n">
-        <v>46098.875</v>
+        <v>46098.70833333334</v>
       </c>
     </row>
     <row r="59">
@@ -11977,12 +11977,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12165,7 +12165,7 @@
         <v>0</v>
       </c>
       <c r="BI59" s="3" t="n">
-        <v>46098.875</v>
+        <v>46098.70833333334</v>
       </c>
     </row>
     <row r="60">
@@ -12174,27 +12174,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12362,7 +12362,7 @@
         <v>0</v>
       </c>
       <c r="BI60" s="3" t="n">
-        <v>46098.875</v>
+        <v>46098.77083333334</v>
       </c>
     </row>
     <row r="61">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12953,6 +12953,597 @@
         <v>0</v>
       </c>
       <c r="BI63" s="3" t="n">
+        <v>46098.875</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Xorazm</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Bunyodkor</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N64" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0</v>
+      </c>
+      <c r="X64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI64" s="3" t="n">
+        <v>46098.875</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Kokand-1912</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Navbahor</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N65" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" t="n">
+        <v>0</v>
+      </c>
+      <c r="X65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI65" s="3" t="n">
+        <v>46098.875</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Leones del Norte</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>LDU Quito</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N66" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" t="n">
+        <v>0</v>
+      </c>
+      <c r="W66" t="n">
+        <v>0</v>
+      </c>
+      <c r="X66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI66" s="3" t="n">
         <v>46098.875</v>
       </c>
     </row>

--- a/jogos_2026-03-17.xlsx
+++ b/jogos_2026-03-17.xlsx
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2570,143 +2570,143 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BH11" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="BI11" s="3" t="n">
         <v>46098.625</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,143 +3161,143 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BH14" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="BI14" s="3" t="n">
         <v>46098.625</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G64" t="n">

--- a/jogos_2026-03-17.xlsx
+++ b/jogos_2026-03-17.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI66"/>
+  <dimension ref="A1:BI64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2373,143 +2373,143 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BH10" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="BI10" s="3" t="n">
         <v>46098.625</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2570,143 +2570,143 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="R11" t="n">
-        <v>3.9</v>
+        <v>4.59</v>
       </c>
       <c r="S11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="BI11" s="3" t="n">
         <v>46098.625</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3640,10 +3640,10 @@
         <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
         <v>0</v>
@@ -3655,10 +3655,10 @@
         <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4034,10 +4034,10 @@
         <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AS18" t="n">
         <v>0</v>
@@ -4049,10 +4049,10 @@
         <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>46098.64583333334</v>
+        <v>46098.66666666666</v>
       </c>
     </row>
     <row r="21">
@@ -4491,12 +4491,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>46098.64583333334</v>
+        <v>46098.66666666666</v>
       </c>
     </row>
     <row r="22">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6649,7 +6649,7 @@
         <v>0</v>
       </c>
       <c r="BI31" s="3" t="n">
-        <v>46098.66666666666</v>
+        <v>46098.6875</v>
       </c>
     </row>
     <row r="32">
@@ -6658,12 +6658,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6846,7 +6846,7 @@
         <v>0</v>
       </c>
       <c r="BI32" s="3" t="n">
-        <v>46098.66666666666</v>
+        <v>46098.69791666666</v>
       </c>
     </row>
     <row r="33">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
         <v>0</v>
       </c>
       <c r="BI33" s="3" t="n">
-        <v>46098.6875</v>
+        <v>46098.69791666666</v>
       </c>
     </row>
     <row r="34">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="R47" t="n">
-        <v>3.38</v>
+        <v>3.05</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>5.73</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10992,12 +10992,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11180,7 +11180,7 @@
         <v>0</v>
       </c>
       <c r="BI54" s="3" t="n">
-        <v>46098.69791666666</v>
+        <v>46098.70833333334</v>
       </c>
     </row>
     <row r="55">
@@ -11189,12 +11189,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11377,7 +11377,7 @@
         <v>0</v>
       </c>
       <c r="BI55" s="3" t="n">
-        <v>46098.69791666666</v>
+        <v>46098.70833333334</v>
       </c>
     </row>
     <row r="56">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11780,27 +11780,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11968,7 +11968,7 @@
         <v>0</v>
       </c>
       <c r="BI58" s="3" t="n">
-        <v>46098.70833333334</v>
+        <v>46098.77083333334</v>
       </c>
     </row>
     <row r="59">
@@ -11977,27 +11977,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12165,7 +12165,7 @@
         <v>0</v>
       </c>
       <c r="BI59" s="3" t="n">
-        <v>46098.70833333334</v>
+        <v>46098.875</v>
       </c>
     </row>
     <row r="60">
@@ -12174,27 +12174,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12223,7 +12223,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P60" t="n">
@@ -12362,7 +12362,7 @@
         <v>0</v>
       </c>
       <c r="BI60" s="3" t="n">
-        <v>46098.77083333334</v>
+        <v>46098.875</v>
       </c>
     </row>
     <row r="61">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13150,400 +13150,6 @@
         <v>0</v>
       </c>
       <c r="BI64" s="3" t="n">
-        <v>46098.875</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Kokand-1912</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Navbahor</t>
-        </is>
-      </c>
-      <c r="G65" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N65" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" t="n">
-        <v>0</v>
-      </c>
-      <c r="S65" t="n">
-        <v>0</v>
-      </c>
-      <c r="T65" t="n">
-        <v>0</v>
-      </c>
-      <c r="U65" t="n">
-        <v>0</v>
-      </c>
-      <c r="V65" t="n">
-        <v>0</v>
-      </c>
-      <c r="W65" t="n">
-        <v>0</v>
-      </c>
-      <c r="X65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ65" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA65" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB65" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC65" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD65" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE65" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF65" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG65" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH65" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI65" s="3" t="n">
-        <v>46098.875</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ecuador Primera Categoría Serie A</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Leones del Norte</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>LDU Quito</t>
-        </is>
-      </c>
-      <c r="G66" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N66" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" t="n">
-        <v>0</v>
-      </c>
-      <c r="T66" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" t="n">
-        <v>0</v>
-      </c>
-      <c r="V66" t="n">
-        <v>0</v>
-      </c>
-      <c r="W66" t="n">
-        <v>0</v>
-      </c>
-      <c r="X66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI66" s="3" t="n">
         <v>46098.875</v>
       </c>
     </row>

--- a/jogos_2026-03-17.xlsx
+++ b/jogos_2026-03-17.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI64"/>
+  <dimension ref="A1:BI67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1527,7 +1527,7 @@
         <v>0</v>
       </c>
       <c r="BI5" s="3" t="n">
-        <v>46098.54166666666</v>
+        <v>46098.45833333334</v>
       </c>
     </row>
     <row r="6">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1724,7 +1724,7 @@
         <v>0</v>
       </c>
       <c r="BI6" s="3" t="n">
-        <v>46098.58333333334</v>
+        <v>46098.45833333334</v>
       </c>
     </row>
     <row r="7">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1921,7 +1921,7 @@
         <v>0</v>
       </c>
       <c r="BI7" s="3" t="n">
-        <v>46098.60416666666</v>
+        <v>46098.54166666666</v>
       </c>
     </row>
     <row r="8">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2118,7 +2118,7 @@
         <v>0</v>
       </c>
       <c r="BI8" s="3" t="n">
-        <v>46098.60416666666</v>
+        <v>46098.58333333334</v>
       </c>
     </row>
     <row r="9">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="BI9" s="3" t="n">
-        <v>46098.61458333334</v>
+        <v>46098.60416666666</v>
       </c>
     </row>
     <row r="10">
@@ -2324,12 +2324,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2373,146 +2373,146 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BH10" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="BI10" s="3" t="n">
-        <v>46098.625</v>
+        <v>46098.60416666666</v>
       </c>
     </row>
     <row r="11">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="BI11" s="3" t="n">
-        <v>46098.625</v>
+        <v>46098.61458333334</v>
       </c>
     </row>
     <row r="12">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,146 +3555,146 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BH16" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="BI16" s="3" t="n">
-        <v>46098.64583333334</v>
+        <v>46098.625</v>
       </c>
     </row>
     <row r="17">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="BI17" s="3" t="n">
-        <v>46098.64583333334</v>
+        <v>46098.625</v>
       </c>
     </row>
     <row r="18">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4034,10 +4034,10 @@
         <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
         <v>0</v>
@@ -4049,10 +4049,10 @@
         <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>46098.66666666666</v>
+        <v>46098.64583333334</v>
       </c>
     </row>
     <row r="21">
@@ -4491,12 +4491,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4547,76 +4547,76 @@
         <v>2.55</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="R21" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4625,10 +4625,10 @@
         <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AS21" t="n">
         <v>0</v>
@@ -4640,10 +4640,10 @@
         <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX21" t="n">
         <v>0</v>
@@ -4658,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>46098.66666666666</v>
+        <v>46098.64583333334</v>
       </c>
     </row>
     <row r="22">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6461,12 +6461,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>3.84</v>
+        <v>1.33</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="R31" t="n">
-        <v>1.84</v>
+        <v>8.4</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6649,7 +6649,7 @@
         <v>0</v>
       </c>
       <c r="BI31" s="3" t="n">
-        <v>46098.6875</v>
+        <v>46098.66666666666</v>
       </c>
     </row>
     <row r="32">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6846,7 +6846,7 @@
         <v>0</v>
       </c>
       <c r="BI32" s="3" t="n">
-        <v>46098.69791666666</v>
+        <v>46098.6875</v>
       </c>
     </row>
     <row r="33">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.84</v>
+        <v>2.16</v>
       </c>
       <c r="Q33" t="n">
         <v>3.3</v>
       </c>
       <c r="R33" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.55</v>
+        <v>2.19</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="R34" t="n">
-        <v>2.46</v>
+        <v>3.15</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="R35" t="n">
-        <v>3.05</v>
+        <v>3.64</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.33</v>
+        <v>1.89</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="R36" t="n">
-        <v>2.79</v>
+        <v>3.55</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q37" t="n">
         <v>3.3</v>
       </c>
-      <c r="Q37" t="n">
-        <v>3.2</v>
-      </c>
       <c r="R37" t="n">
-        <v>2.1</v>
+        <v>2.79</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="R38" t="n">
-        <v>4.25</v>
+        <v>5.73</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.04</v>
+        <v>2.34</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="R39" t="n">
-        <v>3.38</v>
+        <v>2.84</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.34</v>
+        <v>1.68</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="R40" t="n">
-        <v>2.84</v>
+        <v>4.25</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.75</v>
+        <v>2.48</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="R42" t="n">
-        <v>4.25</v>
+        <v>2.6</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="R43" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.5</v>
+        <v>1.69</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="R45" t="n">
-        <v>2.6</v>
+        <v>4.33</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.16</v>
+        <v>2.84</v>
       </c>
       <c r="Q47" t="n">
         <v>3.3</v>
       </c>
       <c r="R47" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.8</v>
+        <v>2.55</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R48" t="n">
-        <v>4</v>
+        <v>2.46</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="Q49" t="n">
         <v>3.15</v>
       </c>
       <c r="R49" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.89</v>
+        <v>2.5</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="R50" t="n">
-        <v>3.55</v>
+        <v>2.6</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.48</v>
+        <v>1.78</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R51" t="n">
-        <v>2.6</v>
+        <v>4.06</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.49</v>
+        <v>1.93</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="R52" t="n">
-        <v>5.73</v>
+        <v>3.6</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.88</v>
+        <v>3.3</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="R53" t="n">
-        <v>3.64</v>
+        <v>2.1</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10992,12 +10992,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11180,7 +11180,7 @@
         <v>0</v>
       </c>
       <c r="BI54" s="3" t="n">
-        <v>46098.70833333334</v>
+        <v>46098.69791666666</v>
       </c>
     </row>
     <row r="55">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11780,27 +11780,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11968,7 +11968,7 @@
         <v>0</v>
       </c>
       <c r="BI58" s="3" t="n">
-        <v>46098.77083333334</v>
+        <v>46098.70833333334</v>
       </c>
     </row>
     <row r="59">
@@ -11977,27 +11977,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12165,7 +12165,7 @@
         <v>0</v>
       </c>
       <c r="BI59" s="3" t="n">
-        <v>46098.875</v>
+        <v>46098.75</v>
       </c>
     </row>
     <row r="60">
@@ -12174,12 +12174,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12223,7 +12223,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P60" t="n">
@@ -12362,7 +12362,7 @@
         <v>0</v>
       </c>
       <c r="BI60" s="3" t="n">
-        <v>46098.875</v>
+        <v>46098.75</v>
       </c>
     </row>
     <row r="61">
@@ -12371,12 +12371,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12559,7 +12559,7 @@
         <v>0</v>
       </c>
       <c r="BI61" s="3" t="n">
-        <v>46098.875</v>
+        <v>46098.77083333334</v>
       </c>
     </row>
     <row r="62">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13011,145 +13011,736 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0</v>
+      </c>
+      <c r="X64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI64" s="3" t="n">
+        <v>46098.875</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Qizilqum</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>AGMK</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N65" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="P64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" t="n">
-        <v>0</v>
-      </c>
-      <c r="V64" t="n">
-        <v>0</v>
-      </c>
-      <c r="W64" t="n">
-        <v>0</v>
-      </c>
-      <c r="X64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ64" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA64" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB64" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC64" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD64" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE64" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF64" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG64" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH64" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI64" s="3" t="n">
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" t="n">
+        <v>0</v>
+      </c>
+      <c r="X65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI65" s="3" t="n">
+        <v>46098.875</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Xorazm</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Bunyodkor</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N66" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" t="n">
+        <v>0</v>
+      </c>
+      <c r="W66" t="n">
+        <v>0</v>
+      </c>
+      <c r="X66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI66" s="3" t="n">
+        <v>46098.875</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Turkey Süper Lig</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Rizespor</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Samsunspor</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" t="n">
+        <v>0</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0</v>
+      </c>
+      <c r="X67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI67" s="3" t="n">
         <v>46098.875</v>
       </c>
     </row>

--- a/jogos_2026-03-17.xlsx
+++ b/jogos_2026-03-17.xlsx
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,143 +3555,143 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BH16" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="BI16" s="3" t="n">
         <v>46098.625</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,143 +3752,143 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="R17" t="n">
-        <v>4.59</v>
+        <v>3.9</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BH17" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="BI17" s="3" t="n">
         <v>46098.625</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.02</v>
+        <v>2.55</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="R26" t="n">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.26</v>
+        <v>3.02</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R28" t="n">
-        <v>3.12</v>
+        <v>2.31</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>4.1</v>
+        <v>2.26</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R30" t="n">
-        <v>1.89</v>
+        <v>3.12</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.16</v>
+        <v>1.69</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="R33" t="n">
-        <v>3.05</v>
+        <v>4.33</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.19</v>
+        <v>1.78</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="R34" t="n">
-        <v>3.15</v>
+        <v>4.06</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="R36" t="n">
-        <v>3.55</v>
+        <v>4.25</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.33</v>
+        <v>1.8</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R37" t="n">
-        <v>2.79</v>
+        <v>4</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.49</v>
+        <v>2.34</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="R38" t="n">
-        <v>5.73</v>
+        <v>2.84</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.34</v>
+        <v>1.75</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R39" t="n">
-        <v>2.84</v>
+        <v>4.25</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="R40" t="n">
-        <v>4.25</v>
+        <v>5.73</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="R41" t="n">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.48</v>
+        <v>3.3</v>
       </c>
       <c r="Q42" t="n">
         <v>3.2</v>
       </c>
       <c r="R42" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.75</v>
+        <v>2.55</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R43" t="n">
-        <v>4.25</v>
+        <v>2.46</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.69</v>
+        <v>1.89</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="R45" t="n">
-        <v>4.33</v>
+        <v>3.55</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.84</v>
+        <v>2.04</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="R47" t="n">
-        <v>2.3</v>
+        <v>3.38</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="Q48" t="n">
         <v>3.3</v>
       </c>
       <c r="R48" t="n">
-        <v>2.46</v>
+        <v>2.79</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.78</v>
+        <v>2.84</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R51" t="n">
-        <v>4.06</v>
+        <v>2.3</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.93</v>
+        <v>2.48</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R52" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>3.3</v>
+        <v>1.88</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="R53" t="n">
-        <v>2.1</v>
+        <v>3.64</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="R54" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P67" t="n">

--- a/jogos_2026-03-17.xlsx
+++ b/jogos_2026-03-17.xlsx
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,143 +3358,143 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BH15" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="BI15" s="3" t="n">
         <v>46098.625</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,143 +3752,143 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BH17" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="BI17" s="3" t="n">
         <v>46098.625</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.33</v>
+        <v>3.02</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.9</v>
+        <v>3.2</v>
       </c>
       <c r="R29" t="n">
-        <v>8.4</v>
+        <v>2.31</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.69</v>
+        <v>1.49</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="R33" t="n">
-        <v>4.33</v>
+        <v>5.73</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q34" t="n">
         <v>3.5</v>
       </c>
       <c r="R34" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R36" t="n">
         <v>4.25</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q37" t="n">
         <v>3.5</v>
       </c>
       <c r="R37" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.34</v>
+        <v>2.04</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="R38" t="n">
-        <v>2.84</v>
+        <v>3.38</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="R39" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>5.73</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="R41" t="n">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.55</v>
+        <v>2.84</v>
       </c>
       <c r="Q43" t="n">
         <v>3.3</v>
       </c>
       <c r="R43" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.19</v>
+        <v>2.55</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="R44" t="n">
-        <v>3.15</v>
+        <v>2.46</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.89</v>
+        <v>2.48</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="R45" t="n">
-        <v>3.55</v>
+        <v>2.6</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.16</v>
+        <v>1.88</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="R46" t="n">
-        <v>3.05</v>
+        <v>3.64</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.04</v>
+        <v>2.34</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="R47" t="n">
-        <v>3.38</v>
+        <v>2.84</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="R48" t="n">
-        <v>2.79</v>
+        <v>3.15</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="R49" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.84</v>
+        <v>2.16</v>
       </c>
       <c r="Q51" t="n">
         <v>3.3</v>
       </c>
       <c r="R51" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.48</v>
+        <v>1.93</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R52" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.88</v>
+        <v>3.3</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="R53" t="n">
-        <v>3.64</v>
+        <v>2.1</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="R54" t="n">
-        <v>2.6</v>
+        <v>2.79</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G67" t="n">

--- a/jogos_2026-03-17.xlsx
+++ b/jogos_2026-03-17.xlsx
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4034,10 +4034,10 @@
         <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AS18" t="n">
         <v>0</v>
@@ -4049,10 +4049,10 @@
         <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4625,10 +4625,10 @@
         <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
         <v>0</v>
@@ -4640,10 +4640,10 @@
         <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
         <v>0</v>
@@ -4658,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.33</v>
+        <v>3.02</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.9</v>
+        <v>3.2</v>
       </c>
       <c r="R22" t="n">
-        <v>8.4</v>
+        <v>2.31</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.26</v>
+        <v>1.33</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="R24" t="n">
-        <v>3.12</v>
+        <v>8.4</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>3.02</v>
+        <v>2.55</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="R29" t="n">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="R33" t="n">
-        <v>5.73</v>
+        <v>4.25</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.75</v>
+        <v>2.84</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R36" t="n">
-        <v>4.25</v>
+        <v>2.3</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.78</v>
+        <v>2.04</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="R37" t="n">
-        <v>4.06</v>
+        <v>3.38</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.04</v>
+        <v>2.55</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="R38" t="n">
-        <v>3.38</v>
+        <v>2.46</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.69</v>
+        <v>2.33</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="R39" t="n">
-        <v>4.33</v>
+        <v>2.79</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="R41" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.84</v>
+        <v>3.3</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R43" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.55</v>
+        <v>1.89</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="R44" t="n">
-        <v>2.46</v>
+        <v>3.55</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="R46" t="n">
-        <v>3.64</v>
+        <v>4.06</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.34</v>
+        <v>1.75</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R47" t="n">
-        <v>2.84</v>
+        <v>4.25</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.89</v>
+        <v>2.5</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="R49" t="n">
-        <v>3.55</v>
+        <v>2.6</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="R50" t="n">
-        <v>3.05</v>
+        <v>3.64</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.16</v>
+        <v>1.93</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R51" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.93</v>
+        <v>2.16</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R52" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>3.3</v>
+        <v>1.49</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="R53" t="n">
-        <v>2.1</v>
+        <v>5.73</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.33</v>
+        <v>1.8</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R54" t="n">
-        <v>2.79</v>
+        <v>4</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G66" t="n">

--- a/jogos_2026-03-17.xlsx
+++ b/jogos_2026-03-17.xlsx
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,143 +3358,143 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BH15" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="BI15" s="3" t="n">
         <v>46098.625</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,143 +3752,143 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="R17" t="n">
-        <v>4.59</v>
+        <v>3.9</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BH17" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="BI17" s="3" t="n">
         <v>46098.625</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4034,10 +4034,10 @@
         <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
         <v>0</v>
@@ -4049,10 +4049,10 @@
         <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4428,10 +4428,10 @@
         <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AS20" t="n">
         <v>0</v>
@@ -4443,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.55</v>
+        <v>2.26</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R29" t="n">
-        <v>2.55</v>
+        <v>3.12</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>4.1</v>
+        <v>1.33</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.35</v>
+        <v>4.9</v>
       </c>
       <c r="R30" t="n">
-        <v>1.89</v>
+        <v>8.4</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.68</v>
+        <v>2.84</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="R33" t="n">
-        <v>4.25</v>
+        <v>2.3</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.84</v>
+        <v>1.8</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R36" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.04</v>
+        <v>2.55</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="R37" t="n">
-        <v>3.38</v>
+        <v>2.46</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="R38" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.33</v>
+        <v>1.78</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R39" t="n">
-        <v>2.79</v>
+        <v>4.06</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="R40" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="R43" t="n">
-        <v>2.1</v>
+        <v>3.05</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="R44" t="n">
-        <v>3.55</v>
+        <v>4.25</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.48</v>
+        <v>1.49</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="R45" t="n">
-        <v>2.6</v>
+        <v>5.73</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.78</v>
+        <v>2.48</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="R46" t="n">
-        <v>4.06</v>
+        <v>2.6</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="R47" t="n">
-        <v>4.25</v>
+        <v>3.64</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.5</v>
+        <v>1.89</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="R49" t="n">
-        <v>2.6</v>
+        <v>3.55</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="Q50" t="n">
         <v>3.55</v>
       </c>
       <c r="R50" t="n">
-        <v>3.64</v>
+        <v>3.38</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.93</v>
+        <v>2.16</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R51" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.16</v>
+        <v>1.93</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R52" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="R53" t="n">
-        <v>5.73</v>
+        <v>4.25</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P62" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G67" t="n">

--- a/jogos_2026-03-17.xlsx
+++ b/jogos_2026-03-17.xlsx
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,143 +3358,143 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BH15" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="BI15" s="3" t="n">
         <v>46098.625</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,143 +3752,143 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BH17" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="BI17" s="3" t="n">
         <v>46098.625</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4034,10 +4034,10 @@
         <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AS18" t="n">
         <v>0</v>
@@ -4049,10 +4049,10 @@
         <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4428,10 +4428,10 @@
         <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
         <v>0</v>
@@ -4443,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>3.02</v>
+        <v>4.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="R31" t="n">
-        <v>2.31</v>
+        <v>1.89</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.84</v>
+        <v>1.89</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="R33" t="n">
-        <v>2.3</v>
+        <v>3.55</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R34" t="n">
-        <v>2.79</v>
+        <v>2.84</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="R35" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.55</v>
+        <v>1.78</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R37" t="n">
-        <v>2.46</v>
+        <v>4.06</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="Q38" t="n">
         <v>3.15</v>
       </c>
       <c r="R38" t="n">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="R39" t="n">
-        <v>4.06</v>
+        <v>3.64</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="R41" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,10 +8878,10 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="R43" t="n">
         <v>3.05</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.49</v>
+        <v>2.25</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="R45" t="n">
-        <v>5.73</v>
+        <v>3.05</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.48</v>
+        <v>3.3</v>
       </c>
       <c r="Q46" t="n">
         <v>3.2</v>
       </c>
       <c r="R46" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.88</v>
+        <v>2.84</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="R47" t="n">
-        <v>3.64</v>
+        <v>2.3</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.19</v>
+        <v>2.55</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="R48" t="n">
-        <v>3.15</v>
+        <v>2.46</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.89</v>
+        <v>2.33</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="R49" t="n">
-        <v>3.55</v>
+        <v>2.79</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="R50" t="n">
-        <v>3.38</v>
+        <v>4.25</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.16</v>
+        <v>2.48</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R51" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="R52" t="n">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.68</v>
+        <v>2.04</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="R53" t="n">
-        <v>4.25</v>
+        <v>3.38</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>5.73</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G67" t="n">

--- a/jogos_2026-03-17.xlsx
+++ b/jogos_2026-03-17.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,143 +3358,143 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BH15" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="BI15" s="3" t="n">
         <v>46098.625</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,143 +3555,143 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BH16" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="BI16" s="3" t="n">
         <v>46098.625</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.02</v>
+        <v>4.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="R22" t="n">
-        <v>2.31</v>
+        <v>1.89</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.33</v>
+        <v>2.55</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.9</v>
+        <v>3.35</v>
       </c>
       <c r="R23" t="n">
-        <v>8.4</v>
+        <v>2.55</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>4.1</v>
+        <v>3.02</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="R31" t="n">
-        <v>1.89</v>
+        <v>2.31</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="R33" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.34</v>
+        <v>1.88</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="R34" t="n">
-        <v>2.84</v>
+        <v>3.64</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q36" t="n">
         <v>3.5</v>
       </c>
       <c r="R36" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.78</v>
+        <v>2.48</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="R37" t="n">
-        <v>4.06</v>
+        <v>2.6</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.19</v>
+        <v>1.49</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="R38" t="n">
-        <v>3.15</v>
+        <v>5.73</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="R39" t="n">
-        <v>3.64</v>
+        <v>4.25</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="R41" t="n">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="R43" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,10 +9272,10 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="R45" t="n">
         <v>3.05</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3.3</v>
+        <v>2.04</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="R46" t="n">
-        <v>2.1</v>
+        <v>3.38</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.84</v>
+        <v>1.89</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="R47" t="n">
-        <v>2.3</v>
+        <v>3.55</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.55</v>
+        <v>2.84</v>
       </c>
       <c r="Q48" t="n">
         <v>3.3</v>
       </c>
       <c r="R48" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.75</v>
+        <v>2.55</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R50" t="n">
-        <v>4.25</v>
+        <v>2.46</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.48</v>
+        <v>2.33</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R51" t="n">
-        <v>2.6</v>
+        <v>2.79</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.68</v>
+        <v>2.25</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="R52" t="n">
-        <v>4.25</v>
+        <v>3.05</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.04</v>
+        <v>3.3</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="R53" t="n">
-        <v>3.38</v>
+        <v>2.1</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.49</v>
+        <v>1.93</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="R54" t="n">
-        <v>5.73</v>
+        <v>3.6</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P62" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G67" t="n">

--- a/jogos_2026-03-17.xlsx
+++ b/jogos_2026-03-17.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,143 +3555,143 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BH16" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="BI16" s="3" t="n">
         <v>46098.625</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,143 +3752,143 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BH17" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="BI17" s="3" t="n">
         <v>46098.625</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4034,10 +4034,10 @@
         <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
         <v>0</v>
@@ -4049,10 +4049,10 @@
         <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4231,10 +4231,10 @@
         <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AS19" t="n">
         <v>0</v>
@@ -4246,10 +4246,10 @@
         <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4.1</v>
+        <v>2.55</v>
       </c>
       <c r="Q22" t="n">
         <v>3.35</v>
       </c>
       <c r="R22" t="n">
-        <v>1.89</v>
+        <v>2.55</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.26</v>
+        <v>4.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R29" t="n">
-        <v>3.12</v>
+        <v>1.89</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>3.02</v>
+        <v>1.33</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
       <c r="R31" t="n">
-        <v>2.31</v>
+        <v>8.4</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,55 +6908,55 @@
         </is>
       </c>
       <c r="P33" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R33" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF33" t="n">
         <v>1.8</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R33" t="n">
-        <v>4</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="R34" t="n">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.5</v>
+        <v>1.69</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="R35" t="n">
-        <v>2.6</v>
+        <v>4.33</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.48</v>
+        <v>2.16</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R37" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.49</v>
+        <v>1.89</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="R38" t="n">
-        <v>5.73</v>
+        <v>3.55</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.75</v>
+        <v>2.19</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="R39" t="n">
-        <v>4.25</v>
+        <v>3.15</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.34</v>
+        <v>1.88</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="R40" t="n">
-        <v>2.84</v>
+        <v>3.64</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.68</v>
+        <v>2.48</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="R41" t="n">
-        <v>4.25</v>
+        <v>2.6</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.69</v>
+        <v>1.49</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="R42" t="n">
-        <v>4.33</v>
+        <v>5.73</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.19</v>
+        <v>1.8</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="R43" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.16</v>
+        <v>2.84</v>
       </c>
       <c r="Q45" t="n">
         <v>3.3</v>
       </c>
       <c r="R45" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.04</v>
+        <v>1.68</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="R46" t="n">
-        <v>3.38</v>
+        <v>4.25</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.84</v>
+        <v>2.25</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="R48" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="Q50" t="n">
         <v>3.3</v>
       </c>
       <c r="R50" t="n">
-        <v>2.46</v>
+        <v>2.79</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.33</v>
+        <v>3.3</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R51" t="n">
-        <v>2.79</v>
+        <v>2.1</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="R53" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.93</v>
+        <v>2.34</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R54" t="n">
-        <v>3.6</v>
+        <v>2.84</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13405,7 +13405,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G67" t="n">

--- a/jogos_2026-03-17.xlsx
+++ b/jogos_2026-03-17.xlsx
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2625,10 +2625,10 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2767,143 +2767,143 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BH12" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="BI12" s="3" t="n">
         <v>46098.625</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,143 +3752,143 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BH17" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="BI17" s="3" t="n">
         <v>46098.625</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4034,10 +4034,10 @@
         <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AS18" t="n">
         <v>0</v>
@@ -4049,10 +4049,10 @@
         <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4231,10 +4231,10 @@
         <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
         <v>0</v>
@@ -4246,10 +4246,10 @@
         <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.02</v>
+        <v>2.26</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R26" t="n">
-        <v>2.31</v>
+        <v>3.12</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>4.1</v>
+        <v>1.33</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.35</v>
+        <v>4.9</v>
       </c>
       <c r="R29" t="n">
-        <v>1.89</v>
+        <v>8.4</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.26</v>
+        <v>2.55</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R30" t="n">
-        <v>3.12</v>
+        <v>2.55</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.04</v>
+        <v>2.19</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="R33" t="n">
-        <v>3.38</v>
+        <v>3.15</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.93</v>
+        <v>2.55</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R34" t="n">
-        <v>3.6</v>
+        <v>2.46</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="R35" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="R36" t="n">
-        <v>4.06</v>
+        <v>3.55</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.16</v>
+        <v>1.88</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="R37" t="n">
-        <v>3.05</v>
+        <v>3.64</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.19</v>
+        <v>2.84</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="R39" t="n">
-        <v>3.15</v>
+        <v>2.3</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="R40" t="n">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.48</v>
+        <v>2.04</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="R41" t="n">
-        <v>2.6</v>
+        <v>3.38</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.49</v>
+        <v>2.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="R42" t="n">
-        <v>5.73</v>
+        <v>2.6</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.8</v>
+        <v>2.16</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R43" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.84</v>
+        <v>1.75</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R45" t="n">
-        <v>2.3</v>
+        <v>4.25</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R46" t="n">
-        <v>4.25</v>
+        <v>4.06</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.25</v>
+        <v>1.69</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="R48" t="n">
-        <v>3.05</v>
+        <v>4.33</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="R49" t="n">
-        <v>2.46</v>
+        <v>3.05</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.33</v>
+        <v>2.48</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R50" t="n">
-        <v>2.79</v>
+        <v>2.6</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>3.3</v>
+        <v>1.49</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="R51" t="n">
-        <v>2.1</v>
+        <v>5.73</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="R53" t="n">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.34</v>
+        <v>1.68</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="R54" t="n">
-        <v>2.84</v>
+        <v>4.25</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.07</v>
+        <v>1.47</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.4</v>
+        <v>5.74</v>
       </c>
       <c r="R58" t="n">
-        <v>3.19</v>
+        <v>6.15</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11884,10 +11884,10 @@
         <v>0</v>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13405,7 +13405,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P67" t="n">

--- a/jogos_2026-03-17.xlsx
+++ b/jogos_2026-03-17.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2767,143 +2767,143 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="BI12" s="3" t="n">
         <v>46098.625</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,143 +3161,143 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="R14" t="n">
-        <v>4.59</v>
+        <v>3.9</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BH14" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="BI14" s="3" t="n">
         <v>46098.625</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.26</v>
+        <v>2.55</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R26" t="n">
-        <v>3.12</v>
+        <v>2.55</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>4.1</v>
+        <v>1.33</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.35</v>
+        <v>4.9</v>
       </c>
       <c r="R28" t="n">
-        <v>1.89</v>
+        <v>8.4</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.19</v>
+        <v>3.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="R33" t="n">
-        <v>3.15</v>
+        <v>2.1</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.55</v>
+        <v>1.68</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="R34" t="n">
-        <v>2.46</v>
+        <v>4.25</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.8</v>
+        <v>2.84</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R35" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.88</v>
+        <v>2.16</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="R37" t="n">
-        <v>3.64</v>
+        <v>3.05</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.84</v>
+        <v>1.75</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R39" t="n">
-        <v>2.3</v>
+        <v>4.25</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.93</v>
+        <v>2.34</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R40" t="n">
-        <v>3.6</v>
+        <v>2.84</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="R41" t="n">
-        <v>3.38</v>
+        <v>3.05</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="R42" t="n">
-        <v>2.6</v>
+        <v>2.79</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.16</v>
+        <v>2.55</v>
       </c>
       <c r="Q43" t="n">
         <v>3.3</v>
       </c>
       <c r="R43" t="n">
-        <v>3.05</v>
+        <v>2.46</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.75</v>
+        <v>1.49</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="R45" t="n">
-        <v>4.25</v>
+        <v>5.73</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="R46" t="n">
-        <v>4.06</v>
+        <v>3.55</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>3.3</v>
+        <v>1.88</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="R47" t="n">
-        <v>2.1</v>
+        <v>3.64</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="R48" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q49" t="n">
         <v>3.15</v>
       </c>
       <c r="R49" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.48</v>
+        <v>1.78</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R50" t="n">
-        <v>2.6</v>
+        <v>4.06</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.49</v>
+        <v>2.04</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="R51" t="n">
-        <v>5.73</v>
+        <v>3.38</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.33</v>
+        <v>2.48</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R52" t="n">
-        <v>2.79</v>
+        <v>2.6</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.34</v>
+        <v>1.69</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="R53" t="n">
-        <v>2.84</v>
+        <v>4.33</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.68</v>
+        <v>2.19</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="R54" t="n">
-        <v>4.25</v>
+        <v>3.15</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.07</v>
+        <v>1.47</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.4</v>
+        <v>5.74</v>
       </c>
       <c r="R55" t="n">
-        <v>3.19</v>
+        <v>6.15</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11293,10 +11293,10 @@
         <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.33</v>
+        <v>2.07</v>
       </c>
       <c r="Q56" t="n">
-        <v>6.05</v>
+        <v>3.4</v>
       </c>
       <c r="R56" t="n">
-        <v>10</v>
+        <v>3.19</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="Q58" t="n">
-        <v>5.74</v>
+        <v>6.05</v>
       </c>
       <c r="R58" t="n">
-        <v>6.15</v>
+        <v>10</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,16 +11878,16 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG58" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13405,7 +13405,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P67" t="n">

--- a/jogos_2026-03-17.xlsx
+++ b/jogos_2026-03-17.xlsx
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2767,143 +2767,143 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BH12" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="BI12" s="3" t="n">
         <v>46098.625</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,143 +3161,143 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BH14" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="BI14" s="3" t="n">
         <v>46098.625</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4034,10 +4034,10 @@
         <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
         <v>0</v>
@@ -4049,10 +4049,10 @@
         <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4428,10 +4428,10 @@
         <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AS20" t="n">
         <v>0</v>
@@ -4443,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.26</v>
+        <v>3.02</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R24" t="n">
-        <v>3.12</v>
+        <v>2.31</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q33" t="n">
         <v>3.3</v>
       </c>
-      <c r="Q33" t="n">
-        <v>3.2</v>
-      </c>
       <c r="R33" t="n">
-        <v>2.1</v>
+        <v>2.46</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.84</v>
+        <v>2.25</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="R35" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.16</v>
+        <v>2.33</v>
       </c>
       <c r="Q37" t="n">
         <v>3.3</v>
       </c>
       <c r="R37" t="n">
-        <v>3.05</v>
+        <v>2.79</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.93</v>
+        <v>3.3</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R38" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="R39" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.34</v>
+        <v>1.78</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R40" t="n">
-        <v>2.84</v>
+        <v>4.06</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="R41" t="n">
-        <v>3.05</v>
+        <v>3.64</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="R42" t="n">
-        <v>2.79</v>
+        <v>2.6</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.55</v>
+        <v>1.8</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R43" t="n">
-        <v>2.46</v>
+        <v>4</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.49</v>
+        <v>2.19</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="R45" t="n">
-        <v>5.73</v>
+        <v>3.15</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="R46" t="n">
-        <v>3.55</v>
+        <v>4.25</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.88</v>
+        <v>2.48</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="R47" t="n">
-        <v>3.64</v>
+        <v>2.6</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="R48" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="R49" t="n">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.78</v>
+        <v>1.49</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="R50" t="n">
-        <v>4.06</v>
+        <v>5.73</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="R51" t="n">
-        <v>3.38</v>
+        <v>4.25</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.48</v>
+        <v>2.16</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R52" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="R53" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="Q55" t="n">
-        <v>5.74</v>
+        <v>6.05</v>
       </c>
       <c r="R55" t="n">
-        <v>6.15</v>
+        <v>10</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,16 +11287,16 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG55" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.14</v>
+        <v>1.47</v>
       </c>
       <c r="Q57" t="n">
-        <v>4.37</v>
+        <v>5.74</v>
       </c>
       <c r="R57" t="n">
-        <v>3.13</v>
+        <v>6.15</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,16 +11681,16 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.33</v>
+        <v>2.14</v>
       </c>
       <c r="Q58" t="n">
-        <v>6.05</v>
+        <v>4.37</v>
       </c>
       <c r="R58" t="n">
-        <v>10</v>
+        <v>3.13</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AF58" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G67" t="n">

--- a/jogos_2026-03-17.xlsx
+++ b/jogos_2026-03-17.xlsx
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.26</v>
+        <v>4.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R22" t="n">
-        <v>3.12</v>
+        <v>1.89</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.02</v>
+        <v>2.55</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="R24" t="n">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>4.1</v>
+        <v>3.02</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="R29" t="n">
-        <v>1.89</v>
+        <v>2.31</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.55</v>
+        <v>1.88</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="R33" t="n">
-        <v>2.46</v>
+        <v>3.64</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="R35" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="R36" t="n">
-        <v>3.38</v>
+        <v>3.05</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.33</v>
+        <v>1.93</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R37" t="n">
-        <v>2.79</v>
+        <v>3.6</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>3.3</v>
+        <v>2.48</v>
       </c>
       <c r="Q38" t="n">
         <v>3.2</v>
       </c>
       <c r="R38" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.78</v>
+        <v>1.49</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="R40" t="n">
-        <v>4.06</v>
+        <v>5.73</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="R41" t="n">
-        <v>3.64</v>
+        <v>4</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="R42" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Q43" t="n">
         <v>3.5</v>
       </c>
       <c r="R43" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.84</v>
+        <v>2.04</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="R44" t="n">
-        <v>2.3</v>
+        <v>3.38</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.19</v>
+        <v>2.33</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="R45" t="n">
-        <v>3.15</v>
+        <v>2.79</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="R46" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.48</v>
+        <v>3.3</v>
       </c>
       <c r="Q47" t="n">
         <v>3.2</v>
       </c>
       <c r="R47" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.89</v>
+        <v>2.55</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="R48" t="n">
-        <v>3.55</v>
+        <v>2.46</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="R50" t="n">
-        <v>5.73</v>
+        <v>4.25</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,10 +10651,10 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="R52" t="n">
         <v>3.05</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R53" t="n">
-        <v>3.6</v>
+        <v>4.06</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.33</v>
+        <v>2.07</v>
       </c>
       <c r="Q55" t="n">
-        <v>6.05</v>
+        <v>3.4</v>
       </c>
       <c r="R55" t="n">
-        <v>10</v>
+        <v>3.19</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.4</v>
+        <v>4.37</v>
       </c>
       <c r="R56" t="n">
-        <v>3.19</v>
+        <v>3.13</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="Q57" t="n">
-        <v>5.74</v>
+        <v>6.05</v>
       </c>
       <c r="R57" t="n">
-        <v>6.15</v>
+        <v>10</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,16 +11681,16 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG57" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.14</v>
+        <v>1.47</v>
       </c>
       <c r="Q58" t="n">
-        <v>4.37</v>
+        <v>5.74</v>
       </c>
       <c r="R58" t="n">
-        <v>3.13</v>
+        <v>6.15</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,16 +11878,16 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P64" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13405,7 +13405,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G67" t="n">

--- a/jogos_2026-03-17.xlsx
+++ b/jogos_2026-03-17.xlsx
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2767,143 +2767,143 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="BI12" s="3" t="n">
         <v>46098.625</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,143 +3555,143 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BH16" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="BI16" s="3" t="n">
         <v>46098.625</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4.1</v>
+        <v>2.55</v>
       </c>
       <c r="Q22" t="n">
         <v>3.35</v>
       </c>
       <c r="R22" t="n">
-        <v>1.89</v>
+        <v>2.55</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.33</v>
+        <v>4.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.9</v>
+        <v>3.35</v>
       </c>
       <c r="R27" t="n">
-        <v>8.4</v>
+        <v>1.89</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.19</v>
+        <v>1.68</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="R34" t="n">
-        <v>3.15</v>
+        <v>4.25</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="Q35" t="n">
         <v>3.55</v>
       </c>
       <c r="R35" t="n">
-        <v>3.55</v>
+        <v>3.64</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R36" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.93</v>
+        <v>2.48</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R37" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.48</v>
+        <v>1.69</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="R38" t="n">
-        <v>2.6</v>
+        <v>4.33</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.49</v>
+        <v>1.75</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="R40" t="n">
-        <v>5.73</v>
+        <v>4.25</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.8</v>
+        <v>1.49</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="R41" t="n">
-        <v>4</v>
+        <v>5.73</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.84</v>
+        <v>1.8</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R42" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.75</v>
+        <v>3.3</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="R43" t="n">
-        <v>4.25</v>
+        <v>2.1</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="Q44" t="n">
         <v>3.55</v>
       </c>
       <c r="R44" t="n">
-        <v>3.38</v>
+        <v>3.55</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="Q47" t="n">
         <v>3.3</v>
       </c>
-      <c r="Q47" t="n">
-        <v>3.2</v>
-      </c>
       <c r="R47" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.34</v>
+        <v>2.04</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="R49" t="n">
-        <v>2.84</v>
+        <v>3.38</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.68</v>
+        <v>2.5</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="R50" t="n">
-        <v>4.25</v>
+        <v>2.6</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="Q52" t="n">
         <v>3.15</v>
       </c>
       <c r="R52" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R53" t="n">
-        <v>4.06</v>
+        <v>3.6</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="R54" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.4</v>
+        <v>4.37</v>
       </c>
       <c r="R55" t="n">
-        <v>3.19</v>
+        <v>3.13</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.37</v>
+        <v>3.4</v>
       </c>
       <c r="R56" t="n">
-        <v>3.13</v>
+        <v>3.19</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G66" t="n">

--- a/jogos_2026-03-17.xlsx
+++ b/jogos_2026-03-17.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.55</v>
+        <v>2.26</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R22" t="n">
-        <v>2.55</v>
+        <v>3.12</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>4.1</v>
+        <v>2.55</v>
       </c>
       <c r="Q27" t="n">
         <v>3.35</v>
       </c>
       <c r="R27" t="n">
-        <v>1.89</v>
+        <v>2.55</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.88</v>
+        <v>3.3</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="R35" t="n">
-        <v>3.64</v>
+        <v>2.1</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.69</v>
+        <v>1.49</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="R38" t="n">
-        <v>4.33</v>
+        <v>5.73</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="R39" t="n">
-        <v>4.06</v>
+        <v>3.55</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="R40" t="n">
-        <v>4.25</v>
+        <v>3.64</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.49</v>
+        <v>1.69</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="R41" t="n">
-        <v>5.73</v>
+        <v>4.33</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="R42" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R43" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.89</v>
+        <v>2.5</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="R44" t="n">
-        <v>3.55</v>
+        <v>2.6</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.33</v>
+        <v>2.84</v>
       </c>
       <c r="Q45" t="n">
         <v>3.3</v>
       </c>
       <c r="R45" t="n">
-        <v>2.79</v>
+        <v>2.3</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.84</v>
+        <v>2.16</v>
       </c>
       <c r="Q47" t="n">
         <v>3.3</v>
       </c>
       <c r="R47" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.55</v>
+        <v>1.93</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R48" t="n">
-        <v>2.46</v>
+        <v>3.6</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.04</v>
+        <v>1.68</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="R49" t="n">
-        <v>3.38</v>
+        <v>4.25</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.5</v>
+        <v>1.78</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="R50" t="n">
-        <v>2.6</v>
+        <v>4.06</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="R51" t="n">
-        <v>3.05</v>
+        <v>2.46</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.19</v>
+        <v>2.48</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="R52" t="n">
-        <v>3.15</v>
+        <v>2.6</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R53" t="n">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="R54" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.37</v>
+        <v>3.4</v>
       </c>
       <c r="R55" t="n">
-        <v>3.13</v>
+        <v>3.19</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.07</v>
+        <v>1.47</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.4</v>
+        <v>5.74</v>
       </c>
       <c r="R56" t="n">
-        <v>3.19</v>
+        <v>6.15</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11490,10 +11490,10 @@
         <v>0</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.33</v>
+        <v>2.14</v>
       </c>
       <c r="Q57" t="n">
-        <v>6.05</v>
+        <v>4.37</v>
       </c>
       <c r="R57" t="n">
-        <v>10</v>
+        <v>3.13</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AF57" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="Q58" t="n">
-        <v>5.74</v>
+        <v>6.05</v>
       </c>
       <c r="R58" t="n">
-        <v>6.15</v>
+        <v>10</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,16 +11878,16 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG58" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G66" t="n">

--- a/jogos_2026-03-17.xlsx
+++ b/jogos_2026-03-17.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,143 +3358,143 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BH15" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="BI15" s="3" t="n">
         <v>46098.625</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,143 +3555,143 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BH16" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="BI16" s="3" t="n">
         <v>46098.625</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4428,10 +4428,10 @@
         <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
         <v>0</v>
@@ -4443,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4625,10 +4625,10 @@
         <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AS21" t="n">
         <v>0</v>
@@ -4640,10 +4640,10 @@
         <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX21" t="n">
         <v>0</v>
@@ -4658,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>4.1</v>
+        <v>1.33</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.35</v>
+        <v>4.9</v>
       </c>
       <c r="R28" t="n">
-        <v>1.89</v>
+        <v>8.4</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.33</v>
+        <v>2.26</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="R31" t="n">
-        <v>8.4</v>
+        <v>3.12</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>3.3</v>
+        <v>1.78</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R35" t="n">
-        <v>2.1</v>
+        <v>4.06</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="R36" t="n">
-        <v>2.84</v>
+        <v>2.6</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.49</v>
+        <v>3.3</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="R38" t="n">
-        <v>5.73</v>
+        <v>2.1</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.89</v>
+        <v>2.84</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="R39" t="n">
-        <v>3.55</v>
+        <v>2.3</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="R41" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="R42" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.8</v>
+        <v>2.19</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="R43" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="R44" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.84</v>
+        <v>2.55</v>
       </c>
       <c r="Q45" t="n">
         <v>3.3</v>
       </c>
       <c r="R45" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.04</v>
+        <v>1.68</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="R46" t="n">
-        <v>3.38</v>
+        <v>4.25</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.16</v>
+        <v>2.33</v>
       </c>
       <c r="Q47" t="n">
         <v>3.3</v>
       </c>
       <c r="R47" t="n">
-        <v>3.05</v>
+        <v>2.79</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="R48" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.68</v>
+        <v>2.48</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="R49" t="n">
-        <v>4.25</v>
+        <v>2.6</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.78</v>
+        <v>1.49</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="R50" t="n">
-        <v>4.06</v>
+        <v>5.73</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.55</v>
+        <v>2.04</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="R51" t="n">
-        <v>2.46</v>
+        <v>3.38</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.48</v>
+        <v>2.34</v>
       </c>
       <c r="Q52" t="n">
         <v>3.2</v>
       </c>
       <c r="R52" t="n">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.19</v>
+        <v>1.88</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="R54" t="n">
-        <v>3.15</v>
+        <v>3.64</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13405,7 +13405,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G67" t="n">

--- a/jogos_2026-03-17.xlsx
+++ b/jogos_2026-03-17.xlsx
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,143 +3358,143 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BH15" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="BI15" s="3" t="n">
         <v>46098.625</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,143 +3555,143 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BH16" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="BI16" s="3" t="n">
         <v>46098.625</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>4.1</v>
+        <v>2.55</v>
       </c>
       <c r="Q29" t="n">
         <v>3.35</v>
       </c>
       <c r="R29" t="n">
-        <v>1.89</v>
+        <v>2.55</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.26</v>
+        <v>4.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R31" t="n">
-        <v>3.12</v>
+        <v>1.89</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.69</v>
+        <v>1.89</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="R34" t="n">
-        <v>4.33</v>
+        <v>3.55</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.78</v>
+        <v>2.19</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="R35" t="n">
-        <v>4.06</v>
+        <v>3.15</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="R36" t="n">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="R37" t="n">
-        <v>4</v>
+        <v>3.64</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>3.3</v>
+        <v>1.93</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R38" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.84</v>
+        <v>1.78</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R39" t="n">
-        <v>2.3</v>
+        <v>4.06</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R41" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.89</v>
+        <v>3.3</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="R42" t="n">
-        <v>3.55</v>
+        <v>2.1</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.19</v>
+        <v>2.33</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="R43" t="n">
-        <v>3.15</v>
+        <v>2.79</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,10 +9075,10 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="R44" t="n">
         <v>3.05</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.68</v>
+        <v>2.84</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="R46" t="n">
-        <v>4.25</v>
+        <v>2.3</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="Q47" t="n">
         <v>3.3</v>
       </c>
       <c r="R47" t="n">
-        <v>2.79</v>
+        <v>2.46</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.25</v>
+        <v>1.49</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="R48" t="n">
-        <v>3.05</v>
+        <v>5.73</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.48</v>
+        <v>1.75</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R49" t="n">
-        <v>2.6</v>
+        <v>4.25</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>5.73</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.04</v>
+        <v>2.48</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="R51" t="n">
-        <v>3.38</v>
+        <v>2.6</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.34</v>
+        <v>1.69</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="R52" t="n">
-        <v>2.84</v>
+        <v>4.33</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,10 +10848,10 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R53" t="n">
         <v>4.25</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="Q54" t="n">
         <v>3.55</v>
       </c>
       <c r="R54" t="n">
-        <v>3.64</v>
+        <v>3.38</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.07</v>
+        <v>1.47</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.4</v>
+        <v>5.74</v>
       </c>
       <c r="R55" t="n">
-        <v>3.19</v>
+        <v>6.15</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11293,10 +11293,10 @@
         <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.47</v>
+        <v>2.07</v>
       </c>
       <c r="Q56" t="n">
-        <v>5.74</v>
+        <v>3.4</v>
       </c>
       <c r="R56" t="n">
-        <v>6.15</v>
+        <v>3.19</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11490,10 +11490,10 @@
         <v>0</v>
       </c>
       <c r="AG56" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.14</v>
+        <v>1.33</v>
       </c>
       <c r="Q57" t="n">
-        <v>4.37</v>
+        <v>6.05</v>
       </c>
       <c r="R57" t="n">
-        <v>3.13</v>
+        <v>10</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AF57" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.33</v>
+        <v>2.14</v>
       </c>
       <c r="Q58" t="n">
-        <v>6.05</v>
+        <v>4.37</v>
       </c>
       <c r="R58" t="n">
-        <v>10</v>
+        <v>3.13</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AF58" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P67" t="n">

--- a/jogos_2026-03-17.xlsx
+++ b/jogos_2026-03-17.xlsx
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="R2" t="n">
-        <v>2.82</v>
+        <v>2.99</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AF2" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2767,143 +2767,143 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BH12" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="BI12" s="3" t="n">
         <v>46098.625</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,143 +3555,143 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BH16" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="BI16" s="3" t="n">
         <v>46098.625</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4428,10 +4428,10 @@
         <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AS20" t="n">
         <v>0</v>
@@ -4443,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4625,10 +4625,10 @@
         <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
         <v>0</v>
@@ -4640,10 +4640,10 @@
         <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
         <v>0</v>
@@ -4658,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.33</v>
+        <v>4.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.9</v>
+        <v>3.35</v>
       </c>
       <c r="R22" t="n">
-        <v>8.4</v>
+        <v>1.89</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.02</v>
+        <v>2.26</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R24" t="n">
-        <v>2.31</v>
+        <v>3.12</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.26</v>
+        <v>2.55</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R30" t="n">
-        <v>3.12</v>
+        <v>2.55</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.16</v>
+        <v>1.89</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="R33" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.19</v>
+        <v>1.69</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="R35" t="n">
-        <v>3.15</v>
+        <v>4.33</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R36" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.93</v>
+        <v>2.48</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R38" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.78</v>
+        <v>2.55</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R39" t="n">
-        <v>4.06</v>
+        <v>2.46</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="Q40" t="n">
         <v>3.15</v>
       </c>
       <c r="R40" t="n">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="R41" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="Q42" t="n">
         <v>3.3</v>
       </c>
-      <c r="Q42" t="n">
-        <v>3.2</v>
-      </c>
       <c r="R42" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.25</v>
+        <v>1.49</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="R44" t="n">
-        <v>3.05</v>
+        <v>5.73</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.84</v>
+        <v>1.75</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R46" t="n">
-        <v>2.3</v>
+        <v>4.25</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R47" t="n">
-        <v>2.46</v>
+        <v>2.1</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.49</v>
+        <v>1.8</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="R48" t="n">
-        <v>5.73</v>
+        <v>4</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,10 +10454,10 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="R51" t="n">
         <v>2.6</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="R52" t="n">
-        <v>4.33</v>
+        <v>4.06</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.68</v>
+        <v>1.93</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="R53" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.04</v>
+        <v>2.34</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="R54" t="n">
-        <v>3.38</v>
+        <v>2.84</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.47</v>
+        <v>2.07</v>
       </c>
       <c r="Q55" t="n">
-        <v>5.74</v>
+        <v>3.4</v>
       </c>
       <c r="R55" t="n">
-        <v>6.15</v>
+        <v>3.19</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11293,10 +11293,10 @@
         <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.4</v>
+        <v>4.37</v>
       </c>
       <c r="R56" t="n">
-        <v>3.19</v>
+        <v>3.13</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.14</v>
+        <v>1.47</v>
       </c>
       <c r="Q58" t="n">
-        <v>4.37</v>
+        <v>5.74</v>
       </c>
       <c r="R58" t="n">
-        <v>3.13</v>
+        <v>6.15</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,16 +11878,16 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P67" t="n">

--- a/jogos_2026-03-17.xlsx
+++ b/jogos_2026-03-17.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2583,46 +2583,46 @@
         <v>6.6</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AG11" t="n">
         <v>2.2</v>
@@ -2631,76 +2631,76 @@
         <v>1.6</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2767,143 +2767,143 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="BI12" s="3" t="n">
         <v>46098.625</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,143 +2964,143 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BH13" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="BI13" s="3" t="n">
         <v>46098.625</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4034,10 +4034,10 @@
         <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AS18" t="n">
         <v>0</v>
@@ -4049,10 +4049,10 @@
         <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4428,10 +4428,10 @@
         <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
         <v>0</v>
@@ -4443,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>3.02</v>
+        <v>4.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="R28" t="n">
-        <v>2.31</v>
+        <v>1.89</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="Q33" t="n">
         <v>3.55</v>
       </c>
       <c r="R33" t="n">
-        <v>3.55</v>
+        <v>3.38</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="R35" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="R36" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.48</v>
+        <v>2.84</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R38" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="Q39" t="n">
         <v>3.3</v>
       </c>
       <c r="R39" t="n">
-        <v>2.46</v>
+        <v>2.79</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.25</v>
+        <v>1.49</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="R41" t="n">
-        <v>3.05</v>
+        <v>5.73</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.33</v>
+        <v>1.8</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R43" t="n">
-        <v>2.79</v>
+        <v>4</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.49</v>
+        <v>1.89</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="R44" t="n">
-        <v>5.73</v>
+        <v>3.55</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="R45" t="n">
-        <v>3.38</v>
+        <v>2.6</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q46" t="n">
         <v>3.5</v>
       </c>
       <c r="R46" t="n">
-        <v>4.25</v>
+        <v>4.06</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>3.3</v>
+        <v>2.48</v>
       </c>
       <c r="Q47" t="n">
         <v>3.2</v>
       </c>
       <c r="R47" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="R48" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,10 +10257,10 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R50" t="n">
         <v>4.25</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="R51" t="n">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R52" t="n">
-        <v>4.06</v>
+        <v>4.25</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="R53" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R54" t="n">
-        <v>2.84</v>
+        <v>2.46</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.07</v>
+        <v>1.47</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.4</v>
+        <v>5.74</v>
       </c>
       <c r="R55" t="n">
-        <v>3.19</v>
+        <v>6.15</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11293,10 +11293,10 @@
         <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.37</v>
+        <v>3.4</v>
       </c>
       <c r="R56" t="n">
-        <v>3.13</v>
+        <v>3.19</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.47</v>
+        <v>2.14</v>
       </c>
       <c r="Q58" t="n">
-        <v>5.74</v>
+        <v>4.37</v>
       </c>
       <c r="R58" t="n">
-        <v>6.15</v>
+        <v>3.13</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,16 +11878,16 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG58" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P67" t="n">

--- a/jogos_2026-03-17.xlsx
+++ b/jogos_2026-03-17.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,143 +2964,143 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BH13" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="BI13" s="3" t="n">
         <v>46098.625</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,22 +3165,22 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3189,10 +3189,10 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -3204,91 +3204,91 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BB14" t="n">
         <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BD14" t="n">
         <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,143 +3555,143 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="R16" t="n">
-        <v>4.59</v>
+        <v>3.9</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BH16" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="BI16" s="3" t="n">
         <v>46098.625</v>
@@ -3956,7 +3956,7 @@
         <v>2.55</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="R18" t="n">
         <v>2.62</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4822,49 +4822,49 @@
         <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AU22" t="n">
         <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BB22" t="n">
         <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD22" t="n">
         <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,34 +4938,34 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.33</v>
+        <v>3.02</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.9</v>
+        <v>3.2</v>
       </c>
       <c r="R23" t="n">
-        <v>8.4</v>
+        <v>2.31</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -4977,91 +4977,91 @@
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BB23" t="n">
         <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BD23" t="n">
         <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.02</v>
+        <v>1.68</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.2</v>
+        <v>4.13</v>
       </c>
       <c r="R25" t="n">
-        <v>2.31</v>
+        <v>4.09</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,130 +5529,130 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="Q26" t="n">
         <v>3.35</v>
       </c>
       <c r="R26" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
         <v>2.55</v>
       </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>0</v>
-      </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BB26" t="n">
         <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD26" t="n">
         <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5807,49 +5807,49 @@
         <v>0</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AU27" t="n">
         <v>0</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BB27" t="n">
         <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BD27" t="n">
         <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BF27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,130 +5923,130 @@
         </is>
       </c>
       <c r="P28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R28" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W28" t="n">
+        <v>4</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z28" t="n">
         <v>4.1</v>
       </c>
-      <c r="Q28" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="R28" t="n">
+      <c r="AA28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AX28" t="n">
         <v>1.89</v>
       </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>0</v>
-      </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BB28" t="n">
         <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BD28" t="n">
         <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BF28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,22 +6120,22 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -6144,10 +6144,10 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -6159,91 +6159,91 @@
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AT29" t="n">
         <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY29" t="n">
         <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB29" t="n">
         <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD29" t="n">
         <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,34 +6317,34 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -6356,22 +6356,22 @@
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -6380,67 +6380,67 @@
         <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BB30" t="n">
         <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BD30" t="n">
         <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,22 +6514,22 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.26</v>
+        <v>1.33</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="R31" t="n">
-        <v>3.12</v>
+        <v>9</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -6538,10 +6538,10 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -6553,91 +6553,91 @@
         <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BB31" t="n">
         <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD31" t="n">
         <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BF31" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="R34" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="R35" t="n">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.19</v>
+        <v>2.34</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="R36" t="n">
-        <v>3.15</v>
+        <v>2.84</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="R37" t="n">
-        <v>3.64</v>
+        <v>4</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.84</v>
+        <v>1.78</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R38" t="n">
-        <v>2.3</v>
+        <v>4.06</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R39" t="n">
-        <v>2.79</v>
+        <v>4.25</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.8</v>
+        <v>2.48</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="R43" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.89</v>
+        <v>2.33</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="R44" t="n">
-        <v>3.55</v>
+        <v>2.79</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="R45" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="R46" t="n">
-        <v>4.06</v>
+        <v>3.55</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.48</v>
+        <v>1.93</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R47" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3.3</v>
+        <v>1.88</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="R49" t="n">
-        <v>2.1</v>
+        <v>3.64</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.75</v>
+        <v>2.84</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R50" t="n">
-        <v>4.25</v>
+        <v>2.3</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.34</v>
+        <v>3.3</v>
       </c>
       <c r="Q51" t="n">
         <v>3.2</v>
       </c>
       <c r="R51" t="n">
-        <v>2.84</v>
+        <v>2.1</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.68</v>
+        <v>2.25</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="R52" t="n">
-        <v>4.25</v>
+        <v>3.05</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.55</v>
+        <v>2.19</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="R54" t="n">
-        <v>2.46</v>
+        <v>3.15</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.07</v>
+        <v>1.33</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.4</v>
+        <v>6.05</v>
       </c>
       <c r="R56" t="n">
-        <v>3.19</v>
+        <v>10</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.33</v>
+        <v>2.14</v>
       </c>
       <c r="Q57" t="n">
-        <v>6.05</v>
+        <v>4.37</v>
       </c>
       <c r="R57" t="n">
-        <v>10</v>
+        <v>3.13</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AF57" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="Q58" t="n">
-        <v>4.37</v>
+        <v>3.4</v>
       </c>
       <c r="R58" t="n">
-        <v>3.13</v>
+        <v>3.19</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13405,7 +13405,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P67" t="n">

--- a/jogos_2026-03-17.xlsx
+++ b/jogos_2026-03-17.xlsx
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,22 +2771,22 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -2795,10 +2795,10 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
@@ -2810,91 +2810,91 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BB12" t="n">
         <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BD12" t="n">
         <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF12" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,22 +3165,22 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3189,10 +3189,10 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -3204,91 +3204,91 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
         <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
         <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,143 +3358,143 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BH15" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="BI15" s="3" t="n">
         <v>46098.625</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,143 +3555,143 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BH16" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="BI16" s="3" t="n">
         <v>46098.625</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.55</v>
+        <v>4.32</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.1</v>
+        <v>4.47</v>
       </c>
       <c r="R18" t="n">
-        <v>2.62</v>
+        <v>1.58</v>
       </c>
       <c r="S18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4034,10 +4034,10 @@
         <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
         <v>0</v>
@@ -4049,10 +4049,10 @@
         <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>4.32</v>
+        <v>2.55</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.47</v>
+        <v>3.1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.58</v>
+        <v>2.62</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4625,10 +4625,10 @@
         <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AS21" t="n">
         <v>0</v>
@@ -4640,10 +4640,10 @@
         <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX21" t="n">
         <v>0</v>
@@ -4658,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.2</v>
+        <v>4.13</v>
       </c>
       <c r="R22" t="n">
-        <v>4.7</v>
+        <v>4.09</v>
       </c>
       <c r="S22" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4822,49 +4822,49 @@
         <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
         <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
         <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
         <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,130 +4938,130 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.02</v>
+        <v>1.64</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="R23" t="n">
-        <v>2.31</v>
+        <v>4.7</v>
       </c>
       <c r="S23" t="n">
-        <v>3.5</v>
+        <v>2.14</v>
       </c>
       <c r="T23" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="U23" t="n">
-        <v>2.88</v>
+        <v>4.4</v>
       </c>
       <c r="V23" t="n">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="W23" t="n">
-        <v>2.75</v>
+        <v>3.65</v>
       </c>
       <c r="X23" t="n">
-        <v>2.85</v>
+        <v>2.12</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="AD23" t="n">
-        <v>3</v>
+        <v>5.1</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.02</v>
+        <v>1.5</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.68</v>
+        <v>2.35</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.55</v>
+        <v>2.28</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="AI23" t="n">
-        <v>6.5</v>
+        <v>4.1</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.89</v>
+        <v>2.35</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.32</v>
+        <v>2.07</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.64</v>
+        <v>1.28</v>
       </c>
       <c r="AR23" t="n">
-        <v>2.04</v>
+        <v>1.47</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.6</v>
+        <v>1.74</v>
       </c>
       <c r="AT23" t="n">
-        <v>3.4</v>
+        <v>2.12</v>
       </c>
       <c r="AU23" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.08</v>
+        <v>3.3</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.68</v>
+        <v>2.48</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.42</v>
+        <v>1.95</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.26</v>
+        <v>1.62</v>
       </c>
       <c r="AZ23" t="n">
-        <v>2.18</v>
+        <v>1.3</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.8</v>
+        <v>3.85</v>
       </c>
       <c r="BB23" t="n">
         <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.28</v>
+        <v>1.74</v>
       </c>
       <c r="BD23" t="n">
         <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="BF23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,79 +5135,79 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5216,49 +5216,49 @@
         <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AU24" t="n">
         <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BB24" t="n">
         <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BD24" t="n">
         <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BF24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,34 +5332,34 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.68</v>
+        <v>2.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.13</v>
+        <v>3.35</v>
       </c>
       <c r="R25" t="n">
-        <v>4.09</v>
+        <v>3.15</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -5371,40 +5371,40 @@
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5413,49 +5413,49 @@
         <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU25" t="n">
         <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BB25" t="n">
         <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD25" t="n">
         <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,34 +5529,34 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.3</v>
+        <v>1.33</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.35</v>
+        <v>5.2</v>
       </c>
       <c r="R26" t="n">
-        <v>3.15</v>
+        <v>9</v>
       </c>
       <c r="S26" t="n">
-        <v>2.75</v>
+        <v>1.7</v>
       </c>
       <c r="T26" t="n">
-        <v>2.14</v>
+        <v>2.6</v>
       </c>
       <c r="U26" t="n">
-        <v>3.55</v>
+        <v>7</v>
       </c>
       <c r="V26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
@@ -5568,91 +5568,91 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.15</v>
+        <v>4.35</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.96</v>
+        <v>1.57</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.73</v>
+        <v>2.23</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="AI26" t="n">
-        <v>6.25</v>
+        <v>4.25</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AM26" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
         <v>1.29</v>
       </c>
-      <c r="AN26" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ26" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.76</v>
+        <v>1.21</v>
       </c>
       <c r="BA26" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="BB26" t="n">
         <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="BD26" t="n">
         <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.58</v>
+        <v>1.88</v>
       </c>
       <c r="BF26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,130 +5726,130 @@
         </is>
       </c>
       <c r="P27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R27" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W27" t="n">
+        <v>4</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AM27" t="n">
         <v>1.21</v>
       </c>
-      <c r="Q27" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="R27" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U27" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W27" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AI27" t="n">
+      <c r="AN27" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV27" t="n">
         <v>3.15</v>
       </c>
-      <c r="AJ27" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AK27" t="n">
+      <c r="AW27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
         <v>1.58</v>
       </c>
-      <c r="AL27" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>1.57</v>
-      </c>
       <c r="BD27" t="n">
         <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="BF27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,130 +5923,130 @@
         </is>
       </c>
       <c r="P28" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AV28" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q28" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="R28" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U28" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W28" t="n">
-        <v>4</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AG28" t="n">
+      <c r="AW28" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BA28" t="n">
         <v>2</v>
       </c>
-      <c r="AH28" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>2.7</v>
-      </c>
       <c r="BB28" t="n">
         <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.58</v>
+        <v>2.08</v>
       </c>
       <c r="BD28" t="n">
         <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="BF28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,34 +6120,34 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.65</v>
+        <v>4.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="R29" t="n">
-        <v>2.65</v>
+        <v>1.89</v>
       </c>
       <c r="S29" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="T29" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="U29" t="n">
-        <v>3.1</v>
+        <v>2.43</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="X29" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -6159,40 +6159,40 @@
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.35</v>
+        <v>2.85</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.84</v>
+        <v>1.62</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AI29" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.04</v>
+        <v>1.72</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
@@ -6204,13 +6204,13 @@
         <v>1.74</v>
       </c>
       <c r="AR29" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AU29" t="n">
         <v>2.55</v>
@@ -6225,25 +6225,25 @@
         <v>1.36</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.94</v>
+        <v>3</v>
       </c>
       <c r="BA29" t="n">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="BB29" t="n">
         <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="BD29" t="n">
         <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="BF29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,34 +6317,34 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -6356,22 +6356,22 @@
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -6380,67 +6380,67 @@
         <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="BB30" t="n">
         <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="BD30" t="n">
         <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,130 +6514,130 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.33</v>
+        <v>3.02</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="R31" t="n">
-        <v>9</v>
+        <v>2.31</v>
       </c>
       <c r="S31" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="T31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="X31" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AS31" t="n">
         <v>2.6</v>
       </c>
-      <c r="U31" t="n">
-        <v>7</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y31" t="n">
+      <c r="AT31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE31" t="n">
         <v>1.55</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>1.88</v>
       </c>
       <c r="BF31" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.5</v>
+        <v>1.78</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="R34" t="n">
-        <v>2.6</v>
+        <v>4.06</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.68</v>
+        <v>2.34</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="R35" t="n">
-        <v>4.25</v>
+        <v>2.84</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.34</v>
+        <v>1.68</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="R36" t="n">
-        <v>2.84</v>
+        <v>4.25</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="Q38" t="n">
         <v>3.5</v>
       </c>
       <c r="R38" t="n">
-        <v>4.06</v>
+        <v>4.25</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.55</v>
+        <v>2.19</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="R40" t="n">
-        <v>2.46</v>
+        <v>3.15</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.49</v>
+        <v>2.16</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="R41" t="n">
-        <v>5.73</v>
+        <v>3.05</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="R42" t="n">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.48</v>
+        <v>2.04</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="R43" t="n">
-        <v>2.6</v>
+        <v>3.38</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.33</v>
+        <v>1.69</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="R44" t="n">
-        <v>2.79</v>
+        <v>4.33</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.16</v>
+        <v>1.89</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="R45" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.89</v>
+        <v>1.49</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="R46" t="n">
-        <v>3.55</v>
+        <v>5.73</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.93</v>
+        <v>2.55</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R47" t="n">
-        <v>3.6</v>
+        <v>2.46</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.69</v>
+        <v>2.25</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="R48" t="n">
-        <v>4.33</v>
+        <v>3.05</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.88</v>
+        <v>2.48</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="R49" t="n">
-        <v>3.64</v>
+        <v>2.6</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.84</v>
+        <v>1.88</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="R50" t="n">
-        <v>2.3</v>
+        <v>3.64</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="Q51" t="n">
         <v>3.3</v>
       </c>
-      <c r="Q51" t="n">
-        <v>3.2</v>
-      </c>
       <c r="R51" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="R52" t="n">
-        <v>3.05</v>
+        <v>2.1</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.19</v>
+        <v>2.33</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="R54" t="n">
-        <v>3.15</v>
+        <v>2.79</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.47</v>
+        <v>2.14</v>
       </c>
       <c r="Q55" t="n">
-        <v>5.74</v>
+        <v>4.37</v>
       </c>
       <c r="R55" t="n">
-        <v>6.15</v>
+        <v>3.13</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,16 +11287,16 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG55" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="Q57" t="n">
-        <v>4.37</v>
+        <v>3.4</v>
       </c>
       <c r="R57" t="n">
-        <v>3.13</v>
+        <v>3.19</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.07</v>
+        <v>1.47</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.4</v>
+        <v>5.74</v>
       </c>
       <c r="R58" t="n">
-        <v>3.19</v>
+        <v>6.15</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11884,10 +11884,10 @@
         <v>0</v>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13405,7 +13405,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P67" t="n">

--- a/jogos_2026-03-17.xlsx
+++ b/jogos_2026-03-17.xlsx
@@ -801,22 +801,22 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="R2" t="n">
-        <v>2.99</v>
+        <v>2.77</v>
       </c>
       <c r="S2" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="T2" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="U2" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="V2" t="n">
         <v>1.33</v>
@@ -846,10 +846,10 @@
         <v>3.8</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AG2" t="n">
         <v>2.78</v>
@@ -867,13 +867,13 @@
         <v>1.58</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AM2" t="n">
         <v>1.32</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -912,7 +912,7 @@
         <v>1.95</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="BB2" t="n">
         <v>1.18</v>
@@ -1204,70 +1204,70 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,143 +3358,143 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BH15" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="BI15" s="3" t="n">
         <v>46098.625</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,143 +3555,143 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BH16" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="BI16" s="3" t="n">
         <v>46098.625</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,130 +4938,130 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="R23" t="n">
-        <v>4.7</v>
+        <v>4.07</v>
       </c>
       <c r="S23" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="T23" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="U23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W23" t="n">
+        <v>4</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AU23" t="n">
         <v>4.4</v>
       </c>
-      <c r="V23" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W23" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>0</v>
-      </c>
       <c r="AV23" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="BA23" t="n">
-        <v>3.85</v>
+        <v>2.7</v>
       </c>
       <c r="BB23" t="n">
         <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="BD23" t="n">
         <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="BF23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,130 +5135,130 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.21</v>
+        <v>3.02</v>
       </c>
       <c r="Q24" t="n">
-        <v>6.4</v>
+        <v>3.2</v>
       </c>
       <c r="R24" t="n">
-        <v>9.4</v>
+        <v>2.31</v>
       </c>
       <c r="S24" t="n">
-        <v>1.72</v>
+        <v>3.5</v>
       </c>
       <c r="T24" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="U24" t="n">
-        <v>6.25</v>
+        <v>2.88</v>
       </c>
       <c r="V24" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="W24" t="n">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="X24" t="n">
-        <v>1.93</v>
+        <v>2.85</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.76</v>
+        <v>1.36</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.09</v>
+        <v>1.32</v>
       </c>
       <c r="AD24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI24" t="n">
         <v>6.5</v>
       </c>
-      <c r="AE24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>3.15</v>
-      </c>
       <c r="AJ24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN24" t="n">
         <v>1.32</v>
       </c>
-      <c r="AK24" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>2.95</v>
-      </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ24" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AY24" t="n">
         <v>1.26</v>
       </c>
-      <c r="AR24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AZ24" t="n">
-        <v>1.1</v>
+        <v>2.18</v>
       </c>
       <c r="BA24" t="n">
-        <v>8</v>
+        <v>1.8</v>
       </c>
       <c r="BB24" t="n">
         <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.57</v>
+        <v>2.28</v>
       </c>
       <c r="BD24" t="n">
         <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.23</v>
+        <v>1.55</v>
       </c>
       <c r="BF24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,34 +5332,34 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.3</v>
+        <v>1.33</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.35</v>
+        <v>5.2</v>
       </c>
       <c r="R25" t="n">
-        <v>3.15</v>
+        <v>9</v>
       </c>
       <c r="S25" t="n">
-        <v>2.75</v>
+        <v>1.7</v>
       </c>
       <c r="T25" t="n">
-        <v>2.14</v>
+        <v>2.6</v>
       </c>
       <c r="U25" t="n">
-        <v>3.55</v>
+        <v>7</v>
       </c>
       <c r="V25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -5371,91 +5371,91 @@
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.15</v>
+        <v>4.35</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.96</v>
+        <v>1.57</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.73</v>
+        <v>2.23</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="AI25" t="n">
-        <v>6.25</v>
+        <v>4.25</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AM25" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
         <v>1.29</v>
       </c>
-      <c r="AN25" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ25" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.76</v>
+        <v>1.21</v>
       </c>
       <c r="BA25" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="BB25" t="n">
         <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="BD25" t="n">
         <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.58</v>
+        <v>1.88</v>
       </c>
       <c r="BF25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,34 +5529,34 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.33</v>
+        <v>2.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.2</v>
+        <v>3.35</v>
       </c>
       <c r="R26" t="n">
-        <v>9</v>
+        <v>3.15</v>
       </c>
       <c r="S26" t="n">
-        <v>1.7</v>
+        <v>2.75</v>
       </c>
       <c r="T26" t="n">
-        <v>2.6</v>
+        <v>2.14</v>
       </c>
       <c r="U26" t="n">
-        <v>7</v>
+        <v>3.55</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="X26" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
@@ -5568,91 +5568,91 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>4.35</v>
+        <v>3.15</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.57</v>
+        <v>1.96</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.23</v>
+        <v>1.73</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.45</v>
+        <v>3.4</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.47</v>
+        <v>1.26</v>
       </c>
       <c r="AI26" t="n">
-        <v>4.25</v>
+        <v>6.25</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AN26" t="n">
-        <v>3.05</v>
+        <v>1.56</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.21</v>
+        <v>1.76</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="BB26" t="n">
         <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="BD26" t="n">
         <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.88</v>
+        <v>1.58</v>
       </c>
       <c r="BF26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,130 +5726,130 @@
         </is>
       </c>
       <c r="P27" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AV27" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q27" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="R27" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U27" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W27" t="n">
-        <v>4</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AG27" t="n">
+      <c r="AW27" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BA27" t="n">
         <v>2</v>
       </c>
-      <c r="AH27" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>2.7</v>
-      </c>
       <c r="BB27" t="n">
         <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.58</v>
+        <v>2.08</v>
       </c>
       <c r="BD27" t="n">
         <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="BF27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,22 +5923,22 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -5947,10 +5947,10 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
@@ -5962,91 +5962,91 @@
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AR28" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AT28" t="n">
         <v>0</v>
       </c>
       <c r="AU28" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AY28" t="n">
         <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BA28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB28" t="n">
         <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BD28" t="n">
         <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,130 +6120,130 @@
         </is>
       </c>
       <c r="P29" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R29" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W29" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI29" t="n">
         <v>4.1</v>
       </c>
-      <c r="Q29" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="S29" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U29" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W29" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AE29" t="n">
+      <c r="AJ29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AT29" t="n">
         <v>2.12</v>
       </c>
-      <c r="AF29" t="n">
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AY29" t="n">
         <v>1.62</v>
       </c>
-      <c r="AG29" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AQ29" t="n">
+      <c r="AZ29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC29" t="n">
         <v>1.74</v>
       </c>
-      <c r="AR29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AV29" t="n">
+      <c r="BD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE29" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>3</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>1.5</v>
       </c>
       <c r="BF29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,79 +6317,79 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6398,49 +6398,49 @@
         <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AU30" t="n">
         <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BB30" t="n">
         <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BD30" t="n">
         <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BF30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,130 +6514,130 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>3.02</v>
+        <v>4.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="R31" t="n">
-        <v>2.31</v>
+        <v>1.89</v>
       </c>
       <c r="S31" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="T31" t="n">
         <v>2.1</v>
       </c>
       <c r="U31" t="n">
-        <v>2.88</v>
+        <v>2.43</v>
       </c>
       <c r="V31" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="W31" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="X31" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD31" t="n">
         <v>2.85</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="AE31" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AX31" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD31" t="n">
+      <c r="AY31" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AZ31" t="n">
         <v>3</v>
       </c>
-      <c r="AE31" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>2.18</v>
-      </c>
       <c r="BA31" t="n">
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="BB31" t="n">
         <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="BD31" t="n">
         <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="BF31" t="n">
         <v>0</v>
@@ -6711,22 +6711,22 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="R32" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -6735,10 +6735,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -6750,91 +6750,91 @@
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BB32" t="n">
         <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD32" t="n">
         <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,22 +6908,22 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.5</v>
+        <v>1.68</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="R33" t="n">
-        <v>2.6</v>
+        <v>4.24</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -6932,106 +6932,106 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BB33" t="n">
         <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BD33" t="n">
         <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BF33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,79 +7105,79 @@
         </is>
       </c>
       <c r="P34" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W34" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="X34" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK34" t="n">
         <v>1.78</v>
       </c>
-      <c r="Q34" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R34" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>0</v>
-      </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7186,52 +7186,52 @@
         <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU34" t="n">
         <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7311,121 +7311,121 @@
         <v>2.84</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BB35" t="n">
         <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BD35" t="n">
         <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,79 +7499,79 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.68</v>
+        <v>2.3</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R36" t="n">
-        <v>4.25</v>
+        <v>2.85</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
@@ -7580,52 +7580,52 @@
         <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU36" t="n">
         <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,133 +7696,133 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.75</v>
+        <v>2.65</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="R38" t="n">
-        <v>4.25</v>
+        <v>2.6</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,34 +8090,34 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -8129,91 +8129,91 @@
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BB39" t="n">
         <v>0</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD39" t="n">
         <v>0</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BF39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.19</v>
+        <v>1.69</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="R40" t="n">
-        <v>3.15</v>
+        <v>4.33</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,22 +8484,22 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R41" t="n">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -8508,106 +8508,106 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB41" t="n">
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR41" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS41" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU41" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW41" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX41" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AY41" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BA41" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BB41" t="n">
         <v>0</v>
       </c>
       <c r="BC41" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BD41" t="n">
         <v>0</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.93</v>
+        <v>1.55</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="R42" t="n">
-        <v>3.6</v>
+        <v>5.75</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R43" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W43" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="X43" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC43" t="n">
         <v>2.04</v>
       </c>
-      <c r="Q43" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R43" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC43" t="n">
-        <v>0</v>
-      </c>
       <c r="BD43" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF43" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.69</v>
+        <v>1.95</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="R44" t="n">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,22 +9272,22 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.89</v>
+        <v>2.65</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="R45" t="n">
-        <v>3.55</v>
+        <v>2.7</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -9296,10 +9296,10 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z45" t="n">
         <v>0</v>
@@ -9311,91 +9311,91 @@
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN45" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR45" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AS45" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AU45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV45" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AW45" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AX45" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY45" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BA45" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BB45" t="n">
         <v>0</v>
       </c>
       <c r="BC45" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BD45" t="n">
         <v>0</v>
       </c>
       <c r="BE45" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,133 +9469,133 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.49</v>
+        <v>2.66</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.1</v>
+        <v>3.32</v>
       </c>
       <c r="R46" t="n">
-        <v>5.73</v>
+        <v>2.55</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN46" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR46" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS46" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU46" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AV46" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX46" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AY46" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BA46" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BB46" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC46" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD46" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BE46" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF46" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R47" t="n">
-        <v>2.46</v>
+        <v>2.17</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,22 +9863,22 @@
         </is>
       </c>
       <c r="P48" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R48" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="S48" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q48" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="R48" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V48" t="n">
         <v>0</v>
@@ -9887,106 +9887,106 @@
         <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB48" t="n">
         <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR48" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS48" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AU48" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AV48" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW48" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AX48" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AY48" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AZ48" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BA48" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BB48" t="n">
         <v>0</v>
       </c>
       <c r="BC48" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BD48" t="n">
         <v>0</v>
       </c>
       <c r="BE48" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.48</v>
+        <v>2.16</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R49" t="n">
-        <v>2.6</v>
+        <v>3.32</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="Q50" t="n">
         <v>3.55</v>
       </c>
       <c r="R50" t="n">
-        <v>3.64</v>
+        <v>3.38</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,22 +10454,22 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="R51" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V51" t="n">
         <v>0</v>
@@ -10478,106 +10478,106 @@
         <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB51" t="n">
         <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI51" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL51" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM51" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN51" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
       </c>
       <c r="AP51" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR51" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AS51" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AT51" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU51" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AV51" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX51" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AY51" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ51" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BA51" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BB51" t="n">
         <v>0</v>
       </c>
       <c r="BC51" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BD51" t="n">
         <v>0</v>
       </c>
       <c r="BE51" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BF51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>3.3</v>
+        <v>1.95</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R52" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,22 +10848,22 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R53" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V53" t="n">
         <v>0</v>
@@ -10872,10 +10872,10 @@
         <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z53" t="n">
         <v>0</v>
@@ -10887,40 +10887,40 @@
         <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI53" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL53" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM53" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN53" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
@@ -10929,49 +10929,49 @@
         <v>0</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR53" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS53" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AT53" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AU53" t="n">
         <v>0</v>
       </c>
       <c r="AV53" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AW53" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AX53" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AY53" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AZ53" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BA53" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BB53" t="n">
         <v>0</v>
       </c>
       <c r="BC53" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD53" t="n">
         <v>0</v>
       </c>
       <c r="BE53" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BF53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,22 +11045,22 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="Q54" t="n">
         <v>3.3</v>
       </c>
       <c r="R54" t="n">
-        <v>2.79</v>
+        <v>2.55</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V54" t="n">
         <v>0</v>
@@ -11069,10 +11069,10 @@
         <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -11084,40 +11084,40 @@
         <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI54" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK54" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL54" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AM54" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN54" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AO54" t="n">
         <v>0</v>
@@ -11126,49 +11126,49 @@
         <v>0</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR54" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS54" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AT54" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU54" t="n">
         <v>0</v>
       </c>
       <c r="AV54" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW54" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX54" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY54" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ54" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="BA54" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BB54" t="n">
         <v>0</v>
       </c>
       <c r="BC54" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD54" t="n">
         <v>0</v>
       </c>
       <c r="BE54" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.14</v>
+        <v>1.47</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.37</v>
+        <v>5.74</v>
       </c>
       <c r="R55" t="n">
-        <v>3.13</v>
+        <v>6.15</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,16 +11287,16 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.4</v>
+        <v>4.37</v>
       </c>
       <c r="R57" t="n">
-        <v>3.19</v>
+        <v>3.13</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.47</v>
+        <v>2.07</v>
       </c>
       <c r="Q58" t="n">
-        <v>5.74</v>
+        <v>3.4</v>
       </c>
       <c r="R58" t="n">
-        <v>6.15</v>
+        <v>3.19</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11884,10 +11884,10 @@
         <v>0</v>
       </c>
       <c r="AG58" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G67" t="n">

--- a/jogos_2026-03-17.xlsx
+++ b/jogos_2026-03-17.xlsx
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
         <v>3.65</v>
@@ -879,10 +879,10 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AR2" t="n">
         <v>1.73</v>
@@ -891,28 +891,28 @@
         <v>2.14</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.78</v>
+        <v>2.52</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.8</v>
+        <v>4.25</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.67</v>
+        <v>2.92</v>
       </c>
       <c r="AW2" t="n">
         <v>1.96</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.12</v>
+        <v>1.97</v>
       </c>
       <c r="BB2" t="n">
         <v>1.18</v>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="R7" t="n">
         <v>5.6</v>
@@ -1801,40 +1801,40 @@
         <v>2.15</v>
       </c>
       <c r="U7" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="V7" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="W7" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="X7" t="n">
         <v>2.7</v>
       </c>
-      <c r="X7" t="n">
-        <v>2.95</v>
-      </c>
       <c r="Y7" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="Z7" t="n">
-        <v>7</v>
+        <v>6.55</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AC7" t="n">
         <v>1.33</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="AE7" t="n">
         <v>2</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG7" t="n">
         <v>3.6</v>
@@ -1843,76 +1843,76 @@
         <v>1.25</v>
       </c>
       <c r="AI7" t="n">
-        <v>7.5</v>
+        <v>5.4</v>
       </c>
       <c r="AJ7" t="n">
         <v>1.08</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AM7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AY7" t="n">
         <v>1.29</v>
       </c>
-      <c r="AN7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY7" t="n">
+      <c r="AZ7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BB7" t="n">
         <v>1.3</v>
       </c>
-      <c r="AZ7" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.29</v>
-      </c>
       <c r="BC7" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="BD7" t="n">
         <v>3.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1983,19 +1983,19 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="R8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S8" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="T8" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="U8" t="n">
         <v>8</v>
@@ -2007,22 +2007,22 @@
         <v>3.92</v>
       </c>
       <c r="X8" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Z8" t="n">
         <v>4.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AD8" t="n">
         <v>5.3</v>
@@ -2037,7 +2037,7 @@
         <v>2.1</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AI8" t="n">
         <v>3.4</v>
@@ -2046,55 +2046,55 @@
         <v>1.27</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AN8" t="n">
-        <v>4.98</v>
+        <v>5</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="AW8" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.25</v>
+        <v>7.7</v>
       </c>
       <c r="BB8" t="n">
         <v>1.08</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,22 +2771,22 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -2795,10 +2795,10 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
@@ -2810,91 +2810,91 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
         <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,22 +3165,22 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3189,10 +3189,10 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -3204,91 +3204,91 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BB14" t="n">
         <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BD14" t="n">
         <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,143 +3555,143 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BH16" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="BI16" s="3" t="n">
         <v>46098.625</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,143 +3752,143 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BH17" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="BI17" s="3" t="n">
         <v>46098.625</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4034,10 +4034,10 @@
         <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AS18" t="n">
         <v>0</v>
@@ -4049,10 +4049,10 @@
         <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4.32</v>
+        <v>4.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.47</v>
+        <v>4.6</v>
       </c>
       <c r="R19" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4356,124 +4356,124 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4625,10 +4625,10 @@
         <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
         <v>0</v>
@@ -4640,10 +4640,10 @@
         <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
         <v>0</v>
@@ -4658,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,22 +4741,22 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.68</v>
+        <v>1.33</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.13</v>
+        <v>4.9</v>
       </c>
       <c r="R22" t="n">
-        <v>4.09</v>
+        <v>8.4</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -4765,10 +4765,10 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
@@ -4780,91 +4780,91 @@
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BB22" t="n">
         <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD22" t="n">
         <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BF22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,130 +4938,130 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.95</v>
+        <v>2.26</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="R23" t="n">
-        <v>4.07</v>
+        <v>3.11</v>
       </c>
       <c r="S23" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="T23" t="n">
-        <v>2.6</v>
+        <v>2.14</v>
       </c>
       <c r="U23" t="n">
         <v>3.55</v>
       </c>
       <c r="V23" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="W23" t="n">
-        <v>4</v>
+        <v>2.85</v>
       </c>
       <c r="X23" t="n">
-        <v>1.98</v>
+        <v>2.75</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.72</v>
+        <v>1.38</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>6.1</v>
+        <v>3.15</v>
       </c>
       <c r="AE23" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AY23" t="n">
         <v>1.38</v>
       </c>
-      <c r="AF23" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AT23" t="n">
+      <c r="AZ23" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BA23" t="n">
         <v>2.2</v>
       </c>
-      <c r="AU23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>2.7</v>
-      </c>
       <c r="BB23" t="n">
         <v>0</v>
       </c>
       <c r="BC23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" t="n">
         <v>1.58</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>2.2</v>
       </c>
       <c r="BF23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,34 +5135,34 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -5174,91 +5174,91 @@
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
         <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
         <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,34 +5332,34 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.33</v>
+        <v>2.55</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.2</v>
+        <v>3.35</v>
       </c>
       <c r="R25" t="n">
-        <v>9</v>
+        <v>2.55</v>
       </c>
       <c r="S25" t="n">
-        <v>1.7</v>
+        <v>3.05</v>
       </c>
       <c r="T25" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
         <v>2.6</v>
       </c>
-      <c r="U25" t="n">
-        <v>7</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Y25" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -5371,91 +5371,91 @@
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AD25" t="n">
-        <v>4.35</v>
+        <v>3.35</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.57</v>
+        <v>1.84</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.23</v>
+        <v>1.84</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AI25" t="n">
-        <v>4.25</v>
+        <v>5.6</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.78</v>
+        <v>2.04</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.13</v>
+        <v>1.43</v>
       </c>
       <c r="AN25" t="n">
-        <v>3.05</v>
+        <v>1.44</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.82</v>
+        <v>2.18</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.28</v>
+        <v>2.88</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.86</v>
+        <v>1.58</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.21</v>
+        <v>1.94</v>
       </c>
       <c r="BA25" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="BB25" t="n">
         <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="BD25" t="n">
         <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="BF25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,130 +5529,130 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.3</v>
+        <v>3.02</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="R26" t="n">
-        <v>3.15</v>
+        <v>2.31</v>
       </c>
       <c r="S26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W26" t="n">
         <v>2.75</v>
       </c>
-      <c r="T26" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U26" t="n">
+      <c r="X26" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG26" t="n">
         <v>3.55</v>
       </c>
-      <c r="V26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W26" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AH26" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AI26" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AM26" t="n">
         <v>1.29</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.73</v>
+        <v>2.04</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="AT26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU26" t="n">
         <v>2.75</v>
       </c>
-      <c r="AU26" t="n">
-        <v>0</v>
-      </c>
       <c r="AV26" t="n">
-        <v>2.55</v>
+        <v>2.08</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.61</v>
+        <v>1.42</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.76</v>
+        <v>2.18</v>
       </c>
       <c r="BA26" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="BB26" t="n">
         <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="BD26" t="n">
         <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="BF26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,34 +5726,34 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.65</v>
+        <v>4.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="R27" t="n">
-        <v>2.65</v>
+        <v>1.89</v>
       </c>
       <c r="S27" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="T27" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="U27" t="n">
-        <v>3.1</v>
+        <v>2.43</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="X27" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
@@ -5765,40 +5765,40 @@
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.35</v>
+        <v>2.85</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.84</v>
+        <v>1.62</v>
       </c>
       <c r="AG27" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AI27" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.04</v>
+        <v>1.72</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5810,13 +5810,13 @@
         <v>1.74</v>
       </c>
       <c r="AR27" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AU27" t="n">
         <v>2.55</v>
@@ -5831,25 +5831,25 @@
         <v>1.36</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.94</v>
+        <v>3</v>
       </c>
       <c r="BA27" t="n">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="BB27" t="n">
         <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="BD27" t="n">
         <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="BF27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,79 +5923,79 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6004,52 +6004,52 @@
         <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AU28" t="n">
         <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="R29" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="S29" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="T29" t="n">
-        <v>2.55</v>
+        <v>2.17</v>
       </c>
       <c r="U29" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W29" t="n">
+        <v>4</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AU29" t="n">
         <v>4.4</v>
       </c>
-      <c r="V29" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W29" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>0</v>
-      </c>
       <c r="AV29" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="AW29" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="BA29" t="n">
-        <v>3.85</v>
+        <v>2.7</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.21</v>
+        <v>1.62</v>
       </c>
       <c r="Q30" t="n">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="R30" t="n">
-        <v>9.4</v>
+        <v>4.3</v>
       </c>
       <c r="S30" t="n">
-        <v>1.72</v>
+        <v>2.16</v>
       </c>
       <c r="T30" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="U30" t="n">
-        <v>6.25</v>
+        <v>4.22</v>
       </c>
       <c r="V30" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W30" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="X30" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z30" t="n">
         <v>4.2</v>
       </c>
-      <c r="X30" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>3.95</v>
-      </c>
       <c r="AA30" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AD30" t="n">
-        <v>6.5</v>
+        <v>5.45</v>
       </c>
       <c r="AE30" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BF30" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>0</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,130 +6514,130 @@
         </is>
       </c>
       <c r="P31" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>4</v>
+      </c>
+      <c r="R31" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W31" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="X31" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI31" t="n">
         <v>4.1</v>
       </c>
-      <c r="Q31" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="S31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U31" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W31" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="X31" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AE31" t="n">
+      <c r="AJ31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AT31" t="n">
         <v>2.12</v>
       </c>
-      <c r="AF31" t="n">
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AY31" t="n">
         <v>1.62</v>
       </c>
-      <c r="AG31" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AQ31" t="n">
+      <c r="AZ31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC31" t="n">
         <v>1.74</v>
       </c>
-      <c r="AR31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AV31" t="n">
+      <c r="BD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE31" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>3</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>1.5</v>
       </c>
       <c r="BF31" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,22 +6908,22 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.68</v>
+        <v>3.25</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="R33" t="n">
-        <v>4.24</v>
+        <v>2.17</v>
       </c>
       <c r="S33" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -6932,106 +6932,106 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BB33" t="n">
         <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD33" t="n">
         <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BF33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.37</v>
+        <v>1.75</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="R34" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="S34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U34" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG34" t="n">
         <v>2.85</v>
       </c>
-      <c r="T34" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U34" t="n">
+      <c r="AH34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BA34" t="n">
         <v>3.7</v>
       </c>
-      <c r="V34" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W34" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="X34" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>2.2</v>
-      </c>
       <c r="BB34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.27</v>
+        <v>1.97</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,40 +7302,40 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.34</v>
+        <v>2.65</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="R35" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="S35" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="T35" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="U35" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="V35" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="Y35" t="n">
         <v>1.4</v>
       </c>
       <c r="Z35" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>3.3</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG35" t="n">
         <v>3.2</v>
@@ -7359,7 +7359,7 @@
         <v>1.29</v>
       </c>
       <c r="AI35" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AJ35" t="n">
         <v>1.09</v>
@@ -7374,46 +7374,46 @@
         <v>1.28</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AR35" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="AT35" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="AU35" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AZ35" t="n">
-        <v>2.02</v>
+        <v>1.71</v>
       </c>
       <c r="BA35" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="BB35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,79 +7499,79 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R36" t="n">
-        <v>2.85</v>
+        <v>3.32</v>
       </c>
       <c r="S36" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
@@ -7580,52 +7580,52 @@
         <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT36" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
         <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BA36" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD36" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,133 +7696,133 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R37" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="S37" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AT37" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BA37" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="BD37" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W38" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT38" t="n">
         <v>2.65</v>
       </c>
-      <c r="Q38" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="R38" t="n">
+      <c r="AU38" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV38" t="n">
         <v>2.6</v>
       </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>0</v>
-      </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,34 +8090,34 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>3.4</v>
+        <v>1.55</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="R39" t="n">
-        <v>2.17</v>
+        <v>5.75</v>
       </c>
       <c r="S39" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -8129,91 +8129,91 @@
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN39" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AS39" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AT39" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AU39" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AV39" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AZ39" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BB39" t="n">
         <v>0</v>
       </c>
       <c r="BC39" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD39" t="n">
         <v>0</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BF39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,22 +8287,22 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="Q40" t="n">
         <v>3.75</v>
       </c>
       <c r="R40" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -8311,106 +8311,106 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB40" t="n">
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR40" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AS40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU40" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BB40" t="n">
         <v>0</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BD40" t="n">
         <v>0</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BF40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.95</v>
+        <v>2.37</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="R41" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="S41" t="n">
-        <v>2.48</v>
+        <v>2.85</v>
       </c>
       <c r="T41" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W41" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="X41" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BA41" t="n">
         <v>2.2</v>
       </c>
-      <c r="U41" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="V41" t="n">
-        <v>0</v>
-      </c>
-      <c r="W41" t="n">
-        <v>0</v>
-      </c>
-      <c r="X41" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC41" t="n">
+      <c r="BB41" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD41" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BB41" t="n">
-        <v>0</v>
-      </c>
       <c r="BC41" t="n">
-        <v>2.04</v>
+        <v>2.27</v>
       </c>
       <c r="BD41" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="BF41" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,22 +8681,22 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="R42" t="n">
-        <v>5.75</v>
+        <v>4.25</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -8705,106 +8705,106 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB42" t="n">
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BB42" t="n">
         <v>0</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BD42" t="n">
         <v>0</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.9</v>
+        <v>1.68</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R43" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="U43" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AT43" t="n">
         <v>2.38</v>
       </c>
-      <c r="S43" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U43" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W43" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="X43" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE43" t="n">
+      <c r="AU43" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC43" t="n">
         <v>1.79</v>
       </c>
-      <c r="AF43" t="n">
+      <c r="BD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE43" t="n">
         <v>1.89</v>
       </c>
-      <c r="AG43" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN43" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AO43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ43" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BB43" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC43" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BD43" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="BE43" t="n">
-        <v>1.68</v>
-      </c>
       <c r="BF43" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,79 +9075,79 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="Q44" t="n">
         <v>3.5</v>
       </c>
       <c r="R44" t="n">
-        <v>3.8</v>
+        <v>2.85</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
@@ -9156,52 +9156,52 @@
         <v>0</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR44" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU44" t="n">
         <v>0</v>
       </c>
       <c r="AV44" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AW44" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX44" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY44" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BA44" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BB44" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC44" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD44" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE44" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BF44" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,133 +9272,133 @@
         </is>
       </c>
       <c r="P45" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R45" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="S45" t="n">
         <v>2.65</v>
       </c>
-      <c r="Q45" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="R45" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="S45" t="n">
-        <v>3.1</v>
-      </c>
       <c r="T45" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W45" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="X45" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BA45" t="n">
         <v>2.18</v>
       </c>
-      <c r="U45" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK45" t="n">
+      <c r="BB45" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE45" t="n">
         <v>1.68</v>
       </c>
-      <c r="AL45" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AO45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP45" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ45" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AT45" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AU45" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV45" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AW45" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AX45" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AY45" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ45" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BA45" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BB45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC45" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BD45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE45" t="n">
-        <v>1.63</v>
-      </c>
       <c r="BF45" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,133 +9469,133 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.66</v>
+        <v>1.95</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="R46" t="n">
-        <v>2.55</v>
+        <v>3.8</v>
       </c>
       <c r="S46" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN46" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AS46" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AT46" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU46" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AV46" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BA46" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC46" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BD46" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BF46" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,130 +9666,130 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>3.25</v>
+        <v>2.34</v>
       </c>
       <c r="Q47" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R47" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="S47" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W47" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X47" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AT47" t="n">
         <v>3.4</v>
       </c>
-      <c r="R47" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" t="n">
-        <v>0</v>
-      </c>
-      <c r="W47" t="n">
-        <v>0</v>
-      </c>
-      <c r="X47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT47" t="n">
-        <v>0</v>
-      </c>
       <c r="AU47" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AV47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW47" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX47" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY47" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BA47" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BB47" t="n">
         <v>0</v>
       </c>
       <c r="BC47" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BD47" t="n">
         <v>0</v>
       </c>
       <c r="BE47" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,22 +9863,22 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R48" t="n">
-        <v>4.25</v>
+        <v>2.55</v>
       </c>
       <c r="S48" t="n">
-        <v>2.25</v>
+        <v>3.05</v>
       </c>
       <c r="T48" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="U48" t="n">
-        <v>4.4</v>
+        <v>3.05</v>
       </c>
       <c r="V48" t="n">
         <v>0</v>
@@ -9887,106 +9887,106 @@
         <v>0</v>
       </c>
       <c r="X48" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV48" t="n">
         <v>2.55</v>
       </c>
-      <c r="Y48" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK48" t="n">
+      <c r="AW48" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE48" t="n">
         <v>1.71</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AX48" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AY48" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AZ48" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BA48" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BB48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC48" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE48" t="n">
-        <v>1.68</v>
       </c>
       <c r="BF48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,130 +10060,130 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.16</v>
+        <v>3.4</v>
       </c>
       <c r="Q49" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R49" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="S49" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W49" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X49" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU49" t="n">
         <v>3.3</v>
       </c>
-      <c r="R49" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" t="n">
-        <v>0</v>
-      </c>
-      <c r="W49" t="n">
-        <v>0</v>
-      </c>
-      <c r="X49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>0</v>
-      </c>
       <c r="AV49" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AW49" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX49" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AY49" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AZ49" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BA49" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BB49" t="n">
         <v>0</v>
       </c>
       <c r="BC49" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD49" t="n">
         <v>0</v>
       </c>
       <c r="BE49" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BF49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.04</v>
+        <v>1.69</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="R50" t="n">
-        <v>3.38</v>
+        <v>4.33</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,22 +10454,22 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="R51" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="S51" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="T51" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="U51" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="V51" t="n">
         <v>0</v>
@@ -10478,106 +10478,106 @@
         <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="Y51" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ51" t="n">
         <v>1.52</v>
       </c>
-      <c r="Z51" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>1.7</v>
-      </c>
       <c r="BA51" t="n">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="BB51" t="n">
         <v>0</v>
       </c>
       <c r="BC51" t="n">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="BD51" t="n">
         <v>0</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="BF51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="R52" t="n">
-        <v>3.8</v>
+        <v>3.38</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,79 +10848,79 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.75</v>
+        <v>2.9</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R53" t="n">
-        <v>4.5</v>
+        <v>2.38</v>
       </c>
       <c r="S53" t="n">
-        <v>2.3</v>
+        <v>3.54</v>
       </c>
       <c r="T53" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="U53" t="n">
-        <v>4.4</v>
+        <v>2.84</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="X53" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AD53" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AG53" t="n">
-        <v>2.85</v>
+        <v>2.92</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AI53" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AJ53" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AL53" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AM53" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AN53" t="n">
-        <v>1.9</v>
+        <v>1.38</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
@@ -10929,52 +10929,52 @@
         <v>0</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AR53" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AS53" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AT53" t="n">
-        <v>2.43</v>
+        <v>2.23</v>
       </c>
       <c r="AU53" t="n">
         <v>0</v>
       </c>
       <c r="AV53" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="AW53" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="AX53" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AY53" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="AZ53" t="n">
-        <v>1.29</v>
+        <v>2.38</v>
       </c>
       <c r="BA53" t="n">
-        <v>3.7</v>
+        <v>1.63</v>
       </c>
       <c r="BB53" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC53" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="BD53" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="BE53" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="BF53" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,22 +11045,22 @@
         </is>
       </c>
       <c r="P54" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R54" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q54" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R54" t="n">
-        <v>2.55</v>
-      </c>
       <c r="S54" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
         <v>0</v>
@@ -11069,10 +11069,10 @@
         <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -11084,40 +11084,40 @@
         <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI54" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AJ54" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AL54" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AM54" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN54" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AO54" t="n">
         <v>0</v>
@@ -11126,49 +11126,49 @@
         <v>0</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AS54" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AT54" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AU54" t="n">
         <v>0</v>
       </c>
       <c r="AV54" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AW54" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AX54" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AY54" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ54" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="BA54" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="BB54" t="n">
         <v>0</v>
       </c>
       <c r="BC54" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD54" t="n">
         <v>0</v>
       </c>
       <c r="BE54" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BF54" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.33</v>
+        <v>2.07</v>
       </c>
       <c r="Q56" t="n">
-        <v>6.05</v>
+        <v>3.4</v>
       </c>
       <c r="R56" t="n">
-        <v>10</v>
+        <v>3.19</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.14</v>
+        <v>1.33</v>
       </c>
       <c r="Q57" t="n">
-        <v>4.37</v>
+        <v>6.05</v>
       </c>
       <c r="R57" t="n">
-        <v>3.13</v>
+        <v>10</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AF57" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.4</v>
+        <v>4.37</v>
       </c>
       <c r="R58" t="n">
-        <v>3.19</v>
+        <v>3.13</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P67" t="n">

--- a/jogos_2026-03-17.xlsx
+++ b/jogos_2026-03-17.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI67"/>
+  <dimension ref="A1:BI65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.65</v>
+        <v>3.46</v>
       </c>
       <c r="R2" t="n">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="S2" t="n">
         <v>2.79</v>
@@ -873,7 +873,7 @@
         <v>1.32</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -1204,70 +1204,70 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="BI11" s="3" t="n">
-        <v>46098.61458333334</v>
+        <v>46098.60416666666</v>
       </c>
     </row>
     <row r="12">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="BI12" s="3" t="n">
-        <v>46098.625</v>
+        <v>46098.61458333334</v>
       </c>
     </row>
     <row r="13">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,22 +3165,22 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3189,10 +3189,10 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -3204,91 +3204,91 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
         <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
         <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,22 +3362,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -3386,10 +3386,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -3401,91 +3401,91 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BB15" t="n">
         <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BD15" t="n">
         <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,143 +3752,143 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BH17" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="BI17" s="3" t="n">
         <v>46098.625</v>
@@ -3900,12 +3900,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,146 +3949,146 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.6</v>
+        <v>1.71</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="R18" t="n">
-        <v>2.65</v>
+        <v>4.37</v>
       </c>
       <c r="S18" t="n">
-        <v>3.1</v>
+        <v>2.16</v>
       </c>
       <c r="T18" t="n">
-        <v>1.93</v>
+        <v>2.5</v>
       </c>
       <c r="U18" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="V18" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="W18" t="n">
-        <v>2.5</v>
+        <v>3.52</v>
       </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>2.18</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>1.66</v>
       </c>
       <c r="Z18" t="n">
-        <v>8</v>
+        <v>4.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.4</v>
+        <v>1.16</v>
       </c>
       <c r="AD18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV18" t="n">
         <v>2.75</v>
       </c>
-      <c r="AE18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AW18" t="n">
-        <v>1.74</v>
+        <v>2.08</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BB18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BF18" t="n">
         <v>1.3</v>
       </c>
-      <c r="BC18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>1.12</v>
-      </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BH18" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="BI18" s="3" t="n">
-        <v>46098.64583333334</v>
+        <v>46098.625</v>
       </c>
     </row>
     <row r="19">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S20" t="n">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="T20" t="n">
-        <v>2.42</v>
+        <v>1.93</v>
       </c>
       <c r="U20" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="V20" t="n">
-        <v>1.21</v>
+        <v>1.48</v>
       </c>
       <c r="W20" t="n">
-        <v>3.58</v>
+        <v>2.5</v>
       </c>
       <c r="X20" t="n">
-        <v>2.11</v>
+        <v>3</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.09</v>
+        <v>1.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>5.3</v>
+        <v>2.75</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.41</v>
+        <v>2.2</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.52</v>
+        <v>1.62</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.11</v>
+        <v>4</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.65</v>
+        <v>1.22</v>
       </c>
       <c r="AI20" t="n">
-        <v>3.34</v>
+        <v>8.25</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.24</v>
+        <v>1.05</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.45</v>
+        <v>1.96</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.53</v>
+        <v>1.81</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.16</v>
+        <v>1.38</v>
       </c>
       <c r="AN20" t="n">
-        <v>2.04</v>
+        <v>1.48</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.64</v>
+        <v>2.4</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.35</v>
+        <v>3.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.11</v>
+        <v>1.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4688,12 +4688,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.33</v>
+        <v>4.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="R22" t="n">
-        <v>8.4</v>
+        <v>1.55</v>
       </c>
       <c r="S22" t="n">
-        <v>1.7</v>
+        <v>4.38</v>
       </c>
       <c r="T22" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="U22" t="n">
-        <v>7</v>
+        <v>2.02</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="X22" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="AD22" t="n">
-        <v>4.35</v>
+        <v>7.7</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.57</v>
+        <v>1.24</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.23</v>
+        <v>3.34</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.45</v>
+        <v>1.73</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.47</v>
+        <v>1.99</v>
       </c>
       <c r="AI22" t="n">
-        <v>4.25</v>
+        <v>2.56</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.86</v>
+        <v>1.32</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.78</v>
+        <v>3.05</v>
       </c>
       <c r="AM22" t="n">
         <v>1.13</v>
       </c>
       <c r="AN22" t="n">
-        <v>3.05</v>
+        <v>1.14</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ22" t="n">
         <v>1.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.82</v>
+        <v>2.12</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.95</v>
+        <v>3.18</v>
       </c>
       <c r="AU22" t="n">
-        <v>3.2</v>
+        <v>3.29</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.21</v>
+        <v>2.52</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.5</v>
+        <v>1.85</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.88</v>
+        <v>2.48</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
-        <v>46098.66666666666</v>
+        <v>46098.64583333334</v>
       </c>
     </row>
     <row r="23">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,34 +4938,34 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.26</v>
+        <v>1.33</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="R23" t="n">
-        <v>3.11</v>
+        <v>8.4</v>
       </c>
       <c r="S23" t="n">
-        <v>2.75</v>
+        <v>1.7</v>
       </c>
       <c r="T23" t="n">
-        <v>2.14</v>
+        <v>2.6</v>
       </c>
       <c r="U23" t="n">
-        <v>3.55</v>
+        <v>7</v>
       </c>
       <c r="V23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -4977,91 +4977,91 @@
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.15</v>
+        <v>4.35</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.96</v>
+        <v>1.57</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.73</v>
+        <v>2.23</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="AI23" t="n">
-        <v>6.25</v>
+        <v>4.25</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AM23" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
         <v>1.29</v>
       </c>
-      <c r="AN23" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ23" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.76</v>
+        <v>1.21</v>
       </c>
       <c r="BA23" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="BB23" t="n">
         <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="BD23" t="n">
         <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.58</v>
+        <v>1.88</v>
       </c>
       <c r="BF23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,34 +5135,34 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -5174,40 +5174,40 @@
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5216,49 +5216,49 @@
         <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU24" t="n">
         <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BB24" t="n">
         <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD24" t="n">
         <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,34 +5332,34 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.55</v>
+        <v>4.1</v>
       </c>
       <c r="Q25" t="n">
         <v>3.35</v>
       </c>
       <c r="R25" t="n">
-        <v>2.55</v>
+        <v>1.89</v>
       </c>
       <c r="S25" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="T25" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="U25" t="n">
-        <v>3.1</v>
+        <v>2.43</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="X25" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -5371,40 +5371,40 @@
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.35</v>
+        <v>2.85</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.84</v>
+        <v>1.62</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AI25" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.04</v>
+        <v>1.72</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5416,13 +5416,13 @@
         <v>1.74</v>
       </c>
       <c r="AR25" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AU25" t="n">
         <v>2.55</v>
@@ -5437,25 +5437,25 @@
         <v>1.36</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.94</v>
+        <v>3</v>
       </c>
       <c r="BA25" t="n">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="BB25" t="n">
         <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="BD25" t="n">
         <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="BF25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,130 +5529,130 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.02</v>
+        <v>2.55</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="R26" t="n">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="S26" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="T26" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="U26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS26" t="n">
         <v>2.88</v>
       </c>
-      <c r="V26" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W26" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Y26" t="n">
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AX26" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV26" t="n">
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="n">
         <v>2.08</v>
       </c>
-      <c r="AW26" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>2.28</v>
-      </c>
       <c r="BD26" t="n">
         <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="BF26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,34 +5726,34 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
@@ -5765,22 +5765,22 @@
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -5789,67 +5789,67 @@
         <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AR27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AT27" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AU27" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AZ27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="BB27" t="n">
         <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="BD27" t="n">
         <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.27</v>
+        <v>3.02</v>
       </c>
       <c r="Q28" t="n">
-        <v>6.3</v>
+        <v>3.2</v>
       </c>
       <c r="R28" t="n">
-        <v>7.85</v>
+        <v>2.31</v>
       </c>
       <c r="S28" t="n">
-        <v>1.72</v>
+        <v>3.5</v>
       </c>
       <c r="T28" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="U28" t="n">
-        <v>6.25</v>
+        <v>2.88</v>
       </c>
       <c r="V28" t="n">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="W28" t="n">
-        <v>4.1</v>
+        <v>2.75</v>
       </c>
       <c r="X28" t="n">
-        <v>1.93</v>
+        <v>2.85</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.76</v>
+        <v>1.36</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.09</v>
+        <v>1.32</v>
       </c>
       <c r="AD28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI28" t="n">
         <v>6.5</v>
       </c>
-      <c r="AE28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>2.88</v>
-      </c>
       <c r="AJ28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN28" t="n">
         <v>1.32</v>
       </c>
-      <c r="AK28" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>2.95</v>
-      </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.44</v>
+        <v>2.04</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.06</v>
+        <v>3.4</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV28" t="n">
-        <v>3.4</v>
+        <v>2.08</v>
       </c>
       <c r="AW28" t="n">
-        <v>2.55</v>
+        <v>1.68</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.86</v>
+        <v>1.42</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.66</v>
+        <v>1.26</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.11</v>
+        <v>2.18</v>
       </c>
       <c r="BA28" t="n">
-        <v>8</v>
+        <v>1.8</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.53</v>
+        <v>2.28</v>
       </c>
       <c r="BD28" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>2.32</v>
+        <v>1.55</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="R29" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="S29" t="n">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="T29" t="n">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>3.55</v>
+        <v>4.22</v>
       </c>
       <c r="V29" t="n">
         <v>1.2</v>
       </c>
       <c r="W29" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="X29" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AB29" t="n">
         <v>1.01</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AD29" t="n">
-        <v>6.1</v>
+        <v>5.45</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.85</v>
+        <v>2.66</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AH29" t="n">
         <v>1.74</v>
       </c>
       <c r="AI29" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.73</v>
+        <v>2.63</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR29" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AZ29" t="n">
         <v>1.5</v>
       </c>
-      <c r="AS29" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>1.57</v>
-      </c>
       <c r="BA29" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="BB29" t="n">
         <v>1.1</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="BD29" t="n">
         <v>5.8</v>
       </c>
       <c r="BE29" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="R30" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="S30" t="n">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="T30" t="n">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="U30" t="n">
-        <v>4.22</v>
+        <v>3.55</v>
       </c>
       <c r="V30" t="n">
         <v>1.2</v>
       </c>
       <c r="W30" t="n">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="X30" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AB30" t="n">
         <v>1.01</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>5.45</v>
+        <v>6.1</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.66</v>
+        <v>2.85</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AH30" t="n">
         <v>1.74</v>
       </c>
       <c r="AI30" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AN30" t="n">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AT30" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AV30" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="AW30" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BA30" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="BB30" t="n">
         <v>1.1</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="BD30" t="n">
         <v>5.8</v>
       </c>
       <c r="BE30" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6658,12 +6658,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>4</v>
+        <v>1.27</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.7</v>
+        <v>6.3</v>
       </c>
       <c r="R32" t="n">
-        <v>1.89</v>
+        <v>7.85</v>
       </c>
       <c r="S32" t="n">
-        <v>4.2</v>
+        <v>1.72</v>
       </c>
       <c r="T32" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U32" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE32" t="n">
         <v>2.32</v>
       </c>
-      <c r="U32" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>1.7</v>
-      </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6846,7 +6846,7 @@
         <v>0</v>
       </c>
       <c r="BI32" s="3" t="n">
-        <v>46098.6875</v>
+        <v>46098.66666666666</v>
       </c>
     </row>
     <row r="33">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,22 +6908,22 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="R33" t="n">
-        <v>2.17</v>
+        <v>1.89</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -6932,10 +6932,10 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
@@ -6947,91 +6947,91 @@
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BB33" t="n">
         <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD33" t="n">
         <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF33" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
         <v>0</v>
       </c>
       <c r="BI33" s="3" t="n">
-        <v>46098.69791666666</v>
+        <v>46098.6875</v>
       </c>
     </row>
     <row r="34">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,22 +7105,22 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="R34" t="n">
-        <v>4.5</v>
+        <v>4.14</v>
       </c>
       <c r="S34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -7129,10 +7129,10 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>
@@ -7144,40 +7144,40 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7186,49 +7186,49 @@
         <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
         <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
         <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
         <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.65</v>
+        <v>2.37</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="R35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W35" t="n">
         <v>2.7</v>
       </c>
-      <c r="S35" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U35" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
       <c r="X35" t="n">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="AF35" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK35" t="n">
         <v>1.8</v>
       </c>
-      <c r="AG35" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AL35" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AM35" t="n">
         <v>1.28</v>
       </c>
       <c r="AN35" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
         <v>1.43</v>
       </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ35" t="n">
+      <c r="AR35" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="BE35" t="n">
         <v>1.56</v>
       </c>
-      <c r="AR35" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>1.63</v>
-      </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,130 +7499,130 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.16</v>
+        <v>2.65</v>
       </c>
       <c r="Q36" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD36" t="n">
         <v>3.3</v>
       </c>
-      <c r="R36" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BB36" t="n">
         <v>0</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BD36" t="n">
         <v>0</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,79 +7696,79 @@
         </is>
       </c>
       <c r="P37" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R37" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U37" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF37" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q37" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R37" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>0</v>
-      </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
@@ -7777,49 +7777,49 @@
         <v>0</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AU37" t="n">
         <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BB37" t="n">
         <v>0</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD37" t="n">
         <v>0</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BF37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.32</v>
+        <v>3.45</v>
       </c>
       <c r="R38" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="S38" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AS38" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BA38" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BD38" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,22 +8090,22 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="R39" t="n">
-        <v>5.75</v>
+        <v>4.25</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -8114,106 +8114,106 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BB39" t="n">
         <v>0</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BD39" t="n">
         <v>0</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,22 +8287,22 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="R40" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S40" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -8311,106 +8311,106 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN40" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AS40" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AT40" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AU40" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AV40" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BA40" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="BB40" t="n">
         <v>0</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="BD40" t="n">
         <v>0</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="BF40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.37</v>
+        <v>1.68</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="R41" t="n">
-        <v>3.1</v>
+        <v>4.24</v>
       </c>
       <c r="S41" t="n">
-        <v>2.85</v>
+        <v>2.14</v>
       </c>
       <c r="T41" t="n">
-        <v>2.14</v>
+        <v>2.43</v>
       </c>
       <c r="U41" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="V41" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AV41" t="n">
         <v>2.88</v>
       </c>
-      <c r="Y41" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AW41" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="AY41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ41" t="n">
         <v>1.4</v>
       </c>
-      <c r="AZ41" t="n">
-        <v>1.76</v>
-      </c>
       <c r="BA41" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC41" t="n">
-        <v>2.27</v>
+        <v>1.79</v>
       </c>
       <c r="BD41" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.56</v>
+        <v>1.89</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.75</v>
+        <v>2.66</v>
       </c>
       <c r="Q42" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W42" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="X42" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU42" t="n">
         <v>3.5</v>
       </c>
-      <c r="R42" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U42" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AV42" t="n">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="AW42" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.3</v>
+        <v>1.64</v>
       </c>
       <c r="BA42" t="n">
-        <v>3.95</v>
+        <v>2.5</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC42" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,22 +8878,22 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.68</v>
+        <v>2.16</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="R43" t="n">
-        <v>4.24</v>
+        <v>3.3</v>
       </c>
       <c r="S43" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -8902,106 +8902,106 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AM43" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AT43" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AU43" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AV43" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AW43" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA43" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BB43" t="n">
         <v>0</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD43" t="n">
         <v>0</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BF43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,37 +9075,37 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="Q44" t="n">
         <v>3.5</v>
       </c>
       <c r="R44" t="n">
-        <v>2.85</v>
+        <v>2.3</v>
       </c>
       <c r="S44" t="n">
-        <v>2.9</v>
+        <v>3.52</v>
       </c>
       <c r="T44" t="n">
         <v>2.15</v>
       </c>
       <c r="U44" t="n">
-        <v>3.46</v>
+        <v>2.85</v>
       </c>
       <c r="V44" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W44" t="n">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="X44" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="Z44" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AA44" t="n">
         <v>1.06</v>
@@ -9114,40 +9114,40 @@
         <v>1</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AD44" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="AG44" t="n">
-        <v>2.85</v>
+        <v>2.92</v>
       </c>
       <c r="AH44" t="n">
         <v>1.31</v>
       </c>
       <c r="AI44" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AL44" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AM44" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AN44" t="n">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
@@ -9156,49 +9156,49 @@
         <v>0</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AS44" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AT44" t="n">
-        <v>2.55</v>
+        <v>2.23</v>
       </c>
       <c r="AU44" t="n">
         <v>0</v>
       </c>
       <c r="AV44" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AW44" t="n">
-        <v>2.08</v>
+        <v>2.33</v>
       </c>
       <c r="AX44" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AY44" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AZ44" t="n">
-        <v>1.56</v>
+        <v>2.38</v>
       </c>
       <c r="BA44" t="n">
-        <v>2.55</v>
+        <v>1.63</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="BC44" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="BD44" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="BF44" t="n">
         <v>1.16</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,85 +9272,85 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R45" t="n">
-        <v>3.2</v>
+        <v>2.17</v>
       </c>
       <c r="S45" t="n">
-        <v>2.65</v>
+        <v>3.8</v>
       </c>
       <c r="T45" t="n">
         <v>2.2</v>
       </c>
       <c r="U45" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="V45" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W45" t="n">
-        <v>2.94</v>
+        <v>2.85</v>
       </c>
       <c r="X45" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="Z45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI45" t="n">
         <v>6</v>
       </c>
-      <c r="AA45" t="n">
+      <c r="AJ45" t="n">
         <v>1.09</v>
       </c>
-      <c r="AB45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AK45" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AL45" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="AM45" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN45" t="n">
         <v>1.26</v>
       </c>
-      <c r="AN45" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AO45" t="n">
         <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AQ45" t="n">
         <v>1.48</v>
@@ -9362,7 +9362,7 @@
         <v>2.23</v>
       </c>
       <c r="AT45" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AU45" t="n">
         <v>3.3</v>
@@ -9380,25 +9380,25 @@
         <v>1.35</v>
       </c>
       <c r="AZ45" t="n">
-        <v>1.88</v>
+        <v>2.43</v>
       </c>
       <c r="BA45" t="n">
-        <v>2.18</v>
+        <v>1.65</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC45" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="BD45" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="BF45" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,23 +9469,23 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="R46" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U46" t="n">
         <v>3.8</v>
       </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
       <c r="V46" t="n">
         <v>0</v>
       </c>
@@ -9493,106 +9493,106 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB46" t="n">
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN46" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR46" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AS46" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU46" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AV46" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX46" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AY46" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BA46" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BB46" t="n">
         <v>0</v>
       </c>
       <c r="BC46" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BD46" t="n">
         <v>0</v>
       </c>
       <c r="BE46" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BF46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,67 +9666,67 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.34</v>
+        <v>1.95</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R47" t="n">
-        <v>2.84</v>
+        <v>3.9</v>
       </c>
       <c r="S47" t="n">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="T47" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="U47" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="V47" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Z47" t="n">
-        <v>6.25</v>
+        <v>5.8</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AB47" t="n">
         <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AD47" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AG47" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AI47" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AK47" t="n">
         <v>1.68</v>
@@ -9735,61 +9735,61 @@
         <v>2.02</v>
       </c>
       <c r="AM47" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AN47" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="AR47" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AW47" t="n">
         <v>2.02</v>
       </c>
-      <c r="AS47" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT47" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU47" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AV47" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AW47" t="n">
+      <c r="AX47" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE47" t="n">
         <v>1.68</v>
-      </c>
-      <c r="AX47" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY47" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AZ47" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BA47" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BB47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC47" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BD47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE47" t="n">
-        <v>1.63</v>
       </c>
       <c r="BF47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,133 +9863,133 @@
         </is>
       </c>
       <c r="P48" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R48" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W48" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="X48" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="Y48" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AU48" t="n">
         <v>3.3</v>
       </c>
-      <c r="R48" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S48" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T48" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U48" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="V48" t="n">
-        <v>0</v>
-      </c>
-      <c r="W48" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL48" t="n">
+      <c r="AV48" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BA48" t="n">
         <v>2.18</v>
       </c>
-      <c r="AM48" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AX48" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY48" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ48" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="BA48" t="n">
-        <v>1.87</v>
-      </c>
       <c r="BB48" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC48" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="BD48" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BE48" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="BF48" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,133 +10060,133 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="Q49" t="n">
         <v>3.4</v>
       </c>
       <c r="R49" t="n">
-        <v>2.17</v>
+        <v>3.3</v>
       </c>
       <c r="S49" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="T49" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="U49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W49" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="X49" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV49" t="n">
         <v>2.7</v>
       </c>
-      <c r="V49" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W49" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="X49" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV49" t="n">
-        <v>2.43</v>
-      </c>
       <c r="AW49" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="AX49" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AY49" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AZ49" t="n">
-        <v>2.43</v>
+        <v>1.55</v>
       </c>
       <c r="BA49" t="n">
-        <v>1.65</v>
+        <v>2.75</v>
       </c>
       <c r="BB49" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC49" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="BD49" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BE49" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="BF49" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,130 +10257,130 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.69</v>
+        <v>2.45</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="R50" t="n">
-        <v>4.33</v>
+        <v>2.85</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB50" t="n">
         <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN50" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
       </c>
       <c r="AP50" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR50" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS50" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU50" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AV50" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW50" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX50" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY50" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ50" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BA50" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BB50" t="n">
         <v>0</v>
       </c>
       <c r="BC50" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BD50" t="n">
         <v>0</v>
       </c>
       <c r="BE50" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,22 +10454,22 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R51" t="n">
-        <v>3.9</v>
+        <v>2.55</v>
       </c>
       <c r="S51" t="n">
-        <v>2.48</v>
+        <v>3.05</v>
       </c>
       <c r="T51" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="U51" t="n">
-        <v>3.95</v>
+        <v>3.05</v>
       </c>
       <c r="V51" t="n">
         <v>0</v>
@@ -10478,106 +10478,106 @@
         <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="Z51" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
         <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AD51" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="AG51" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AI51" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="AL51" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="AM51" t="n">
         <v>1.25</v>
       </c>
       <c r="AN51" t="n">
-        <v>1.76</v>
+        <v>1.43</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AS51" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AT51" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AU51" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AV51" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AW51" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AX51" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AY51" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AZ51" t="n">
-        <v>1.52</v>
+        <v>2.07</v>
       </c>
       <c r="BA51" t="n">
-        <v>2.88</v>
+        <v>1.87</v>
       </c>
       <c r="BB51" t="n">
         <v>0</v>
       </c>
       <c r="BC51" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="BD51" t="n">
         <v>0</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="BF51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.04</v>
+        <v>3.35</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="R52" t="n">
-        <v>3.38</v>
+        <v>2.17</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,79 +10848,79 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.9</v>
+        <v>1.72</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R53" t="n">
-        <v>2.38</v>
+        <v>4.5</v>
       </c>
       <c r="S53" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI53" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AJ53" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL53" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM53" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN53" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
@@ -10929,52 +10929,52 @@
         <v>0</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR53" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AS53" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AT53" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AU53" t="n">
         <v>0</v>
       </c>
       <c r="AV53" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AW53" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AX53" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AY53" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ53" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BA53" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BB53" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC53" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="BD53" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="BE53" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BF53" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.65</v>
+        <v>1.88</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.45</v>
+        <v>3.74</v>
       </c>
       <c r="R54" t="n">
-        <v>2.6</v>
+        <v>3.72</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11189,12 +11189,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,79 +11242,79 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.47</v>
+        <v>2.4</v>
       </c>
       <c r="Q55" t="n">
-        <v>5.74</v>
+        <v>3.5</v>
       </c>
       <c r="R55" t="n">
-        <v>6.15</v>
+        <v>2.87</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG55" t="n">
-        <v>2.2</v>
+        <v>2.85</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.6</v>
+        <v>1.31</v>
       </c>
       <c r="AI55" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK55" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL55" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AM55" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN55" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AO55" t="n">
         <v>0</v>
@@ -11323,52 +11323,52 @@
         <v>0</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR55" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU55" t="n">
         <v>0</v>
       </c>
       <c r="AV55" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AW55" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX55" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY55" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AZ55" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BA55" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BB55" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC55" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD55" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE55" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BF55" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11377,7 +11377,7 @@
         <v>0</v>
       </c>
       <c r="BI55" s="3" t="n">
-        <v>46098.70833333334</v>
+        <v>46098.69791666666</v>
       </c>
     </row>
     <row r="56">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,133 +11439,133 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.07</v>
+        <v>1.47</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="R56" t="n">
-        <v>3.19</v>
+        <v>5</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AI56" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK56" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL56" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AM56" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN56" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AO56" t="n">
         <v>0</v>
       </c>
       <c r="AP56" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AR56" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AS56" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AT56" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AU56" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AV56" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AW56" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AX56" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AY56" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AZ56" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BA56" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="BB56" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC56" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BD56" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="BE56" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF56" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,133 +11636,133 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.33</v>
+        <v>2.07</v>
       </c>
       <c r="Q57" t="n">
-        <v>6.05</v>
+        <v>3.9</v>
       </c>
       <c r="R57" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AF57" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW57" t="n">
         <v>2.2</v>
       </c>
-      <c r="AG57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW57" t="n">
-        <v>0</v>
-      </c>
       <c r="AX57" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AY57" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AZ57" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BA57" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BB57" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC57" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BD57" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="BE57" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BF57" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,133 +11833,133 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.14</v>
+        <v>1.3</v>
       </c>
       <c r="Q58" t="n">
-        <v>4.37</v>
+        <v>5.5</v>
       </c>
       <c r="R58" t="n">
-        <v>3.13</v>
+        <v>8.9</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AF58" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI58" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK58" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL58" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AM58" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AN58" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AO58" t="n">
         <v>0</v>
       </c>
       <c r="AP58" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AR58" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AS58" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AT58" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AU58" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AV58" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AW58" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AX58" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AY58" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AZ58" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BA58" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="BB58" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC58" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD58" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE58" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF58" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG58" t="n">
         <v>0</v>
@@ -11977,12 +11977,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12165,7 +12165,7 @@
         <v>0</v>
       </c>
       <c r="BI59" s="3" t="n">
-        <v>46098.75</v>
+        <v>46098.70833333334</v>
       </c>
     </row>
     <row r="60">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12371,27 +12371,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12559,7 +12559,7 @@
         <v>0</v>
       </c>
       <c r="BI61" s="3" t="n">
-        <v>46098.77083333334</v>
+        <v>46098.75</v>
       </c>
     </row>
     <row r="62">
@@ -12568,12 +12568,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12756,7 +12756,7 @@
         <v>0</v>
       </c>
       <c r="BI62" s="3" t="n">
-        <v>46098.875</v>
+        <v>46098.77083333334</v>
       </c>
     </row>
     <row r="63">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P64" t="n">
@@ -13347,400 +13347,6 @@
         <v>0</v>
       </c>
       <c r="BI65" s="3" t="n">
-        <v>46098.875</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Turkey Süper Lig</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Göztepe</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Galatasaray</t>
-        </is>
-      </c>
-      <c r="G66" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N66" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>suspended</t>
-        </is>
-      </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" t="n">
-        <v>0</v>
-      </c>
-      <c r="T66" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" t="n">
-        <v>0</v>
-      </c>
-      <c r="V66" t="n">
-        <v>0</v>
-      </c>
-      <c r="W66" t="n">
-        <v>0</v>
-      </c>
-      <c r="X66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI66" s="3" t="n">
-        <v>46098.875</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Qizilqum</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>AGMK</t>
-        </is>
-      </c>
-      <c r="G67" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N67" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
-      <c r="R67" t="n">
-        <v>0</v>
-      </c>
-      <c r="S67" t="n">
-        <v>0</v>
-      </c>
-      <c r="T67" t="n">
-        <v>0</v>
-      </c>
-      <c r="U67" t="n">
-        <v>0</v>
-      </c>
-      <c r="V67" t="n">
-        <v>0</v>
-      </c>
-      <c r="W67" t="n">
-        <v>0</v>
-      </c>
-      <c r="X67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI67" s="3" t="n">
         <v>46098.875</v>
       </c>
     </row>

--- a/jogos_2026-03-17.xlsx
+++ b/jogos_2026-03-17.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,143 +3358,143 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="R15" t="n">
-        <v>4.58</v>
+        <v>4.37</v>
       </c>
       <c r="S15" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="U15" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X15" t="n">
-        <v>2.65</v>
+        <v>2.18</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.41</v>
+        <v>1.66</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.89</v>
+        <v>1.55</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.79</v>
+        <v>2.28</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.2</v>
+        <v>2.38</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>5.8</v>
+        <v>4.05</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.79</v>
+        <v>1.55</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>1.35</v>
       </c>
-      <c r="AQ15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>1.58</v>
-      </c>
       <c r="BA15" t="n">
-        <v>2.55</v>
+        <v>3.65</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.12</v>
+        <v>1.78</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BH15" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="BI15" s="3" t="n">
         <v>46098.625</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,22 +3756,22 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3780,10 +3780,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -3795,91 +3795,91 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BB17" t="n">
         <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BD17" t="n">
         <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,143 +3949,143 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BH18" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="BI18" s="3" t="n">
         <v>46098.625</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4231,10 +4231,10 @@
         <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AS19" t="n">
         <v>0</v>
@@ -4246,10 +4246,10 @@
         <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4428,10 +4428,10 @@
         <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
         <v>0</v>
@@ -4443,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,34 +4938,34 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.33</v>
+        <v>2.55</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.9</v>
+        <v>3.35</v>
       </c>
       <c r="R23" t="n">
-        <v>8.4</v>
+        <v>2.55</v>
       </c>
       <c r="S23" t="n">
-        <v>1.7</v>
+        <v>3.05</v>
       </c>
       <c r="T23" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
         <v>2.6</v>
       </c>
-      <c r="U23" t="n">
-        <v>7</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Y23" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -4977,91 +4977,91 @@
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AD23" t="n">
-        <v>4.35</v>
+        <v>3.35</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.57</v>
+        <v>1.84</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.23</v>
+        <v>1.84</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AI23" t="n">
-        <v>4.25</v>
+        <v>5.6</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.78</v>
+        <v>2.04</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.13</v>
+        <v>1.43</v>
       </c>
       <c r="AN23" t="n">
-        <v>3.05</v>
+        <v>1.44</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.82</v>
+        <v>2.18</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.28</v>
+        <v>2.88</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.86</v>
+        <v>1.58</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.21</v>
+        <v>1.94</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="BB23" t="n">
         <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="BD23" t="n">
         <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="BF23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,130 +5135,130 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.26</v>
+        <v>3.02</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R24" t="n">
-        <v>3.11</v>
+        <v>2.31</v>
       </c>
       <c r="S24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W24" t="n">
         <v>2.75</v>
       </c>
-      <c r="T24" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U24" t="n">
+      <c r="X24" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG24" t="n">
         <v>3.55</v>
       </c>
-      <c r="V24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W24" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AI24" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AM24" t="n">
         <v>1.29</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.73</v>
+        <v>2.04</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="AT24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU24" t="n">
         <v>2.75</v>
       </c>
-      <c r="AU24" t="n">
-        <v>0</v>
-      </c>
       <c r="AV24" t="n">
-        <v>2.55</v>
+        <v>2.08</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.61</v>
+        <v>1.42</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.76</v>
+        <v>2.18</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="BB24" t="n">
         <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="BD24" t="n">
         <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="BF24" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,130 +5529,130 @@
         </is>
       </c>
       <c r="P26" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R26" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
         <v>2.55</v>
       </c>
-      <c r="Q26" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="R26" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="U26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AW26" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE26" t="n">
         <v>1.58</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>1.65</v>
       </c>
       <c r="BF26" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>3.02</v>
+        <v>1.62</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="R28" t="n">
-        <v>2.31</v>
+        <v>4.3</v>
       </c>
       <c r="S28" t="n">
-        <v>3.5</v>
+        <v>2.16</v>
       </c>
       <c r="T28" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="U28" t="n">
-        <v>2.88</v>
+        <v>4.22</v>
       </c>
       <c r="V28" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="W28" t="n">
-        <v>2.75</v>
+        <v>3.82</v>
       </c>
       <c r="X28" t="n">
-        <v>2.85</v>
+        <v>2.06</v>
       </c>
       <c r="Y28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BF28" t="n">
         <v>1.36</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>0</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="R29" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="S29" t="n">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="T29" t="n">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="U29" t="n">
-        <v>4.22</v>
+        <v>3.55</v>
       </c>
       <c r="V29" t="n">
         <v>1.2</v>
       </c>
       <c r="W29" t="n">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="X29" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AB29" t="n">
         <v>1.01</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>5.45</v>
+        <v>6.1</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.66</v>
+        <v>2.85</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AH29" t="n">
         <v>1.74</v>
       </c>
       <c r="AI29" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AN29" t="n">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="AW29" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BA29" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="BB29" t="n">
         <v>1.1</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="BD29" t="n">
         <v>5.8</v>
       </c>
       <c r="BE29" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,37 +6317,37 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.91</v>
+        <v>1.27</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.4</v>
+        <v>6.3</v>
       </c>
       <c r="R30" t="n">
-        <v>3.4</v>
+        <v>7.85</v>
       </c>
       <c r="S30" t="n">
-        <v>2.38</v>
+        <v>1.72</v>
       </c>
       <c r="T30" t="n">
-        <v>2.17</v>
+        <v>2.9</v>
       </c>
       <c r="U30" t="n">
-        <v>3.55</v>
+        <v>6.25</v>
       </c>
       <c r="V30" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W30" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="X30" t="n">
-        <v>2.11</v>
+        <v>1.93</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="AA30" t="n">
         <v>1.18</v>
@@ -6356,94 +6356,94 @@
         <v>1.01</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AD30" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AI30" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.73</v>
+        <v>2.23</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.83</v>
+        <v>2.95</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AT30" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AU30" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="AW30" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.57</v>
+        <v>1.11</v>
       </c>
       <c r="BA30" t="n">
-        <v>2.7</v>
+        <v>8</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="BD30" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BE30" t="n">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Q32" t="n">
-        <v>6.3</v>
+        <v>4.9</v>
       </c>
       <c r="R32" t="n">
-        <v>7.85</v>
+        <v>8.4</v>
       </c>
       <c r="S32" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="T32" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="U32" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
         <v>1.17</v>
       </c>
-      <c r="W32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AD32" t="n">
-        <v>6.5</v>
+        <v>4.35</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AF32" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT32" t="n">
         <v>2.95</v>
       </c>
-      <c r="AG32" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>2.06</v>
-      </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV32" t="n">
-        <v>3.4</v>
+        <v>2.35</v>
       </c>
       <c r="AW32" t="n">
-        <v>2.55</v>
+        <v>1.86</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.86</v>
+        <v>1.54</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.66</v>
+        <v>1.34</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="BA32" t="n">
-        <v>8</v>
+        <v>4.5</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="BD32" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>2.32</v>
+        <v>1.88</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W34" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="X34" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF34" t="n">
         <v>1.84</v>
       </c>
-      <c r="Q34" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R34" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0</v>
-      </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="Q35" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R35" t="n">
         <v>3.2</v>
       </c>
-      <c r="R35" t="n">
-        <v>3.1</v>
-      </c>
       <c r="S35" t="n">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="T35" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="U35" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="V35" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W35" t="n">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="X35" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AT35" t="n">
         <v>2.88</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="AU35" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY35" t="n">
         <v>1.35</v>
       </c>
-      <c r="Z35" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF35" t="n">
+      <c r="AZ35" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE35" t="n">
         <v>1.68</v>
       </c>
-      <c r="AG35" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>1.56</v>
-      </c>
       <c r="BF35" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,22 +7499,22 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.65</v>
+        <v>1.85</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="R36" t="n">
-        <v>2.7</v>
+        <v>4.25</v>
       </c>
       <c r="S36" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="T36" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="U36" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -7523,106 +7523,106 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AG36" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AI36" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AK36" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE36" t="n">
         <v>1.68</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>1.63</v>
       </c>
       <c r="BF36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,130 +7696,130 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="R37" t="n">
-        <v>4.5</v>
+        <v>2.85</v>
       </c>
       <c r="S37" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="T37" t="n">
-        <v>2.35</v>
+        <v>2.17</v>
       </c>
       <c r="U37" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X37" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB37" t="n">
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AI37" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AL37" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.58</v>
+        <v>2.02</v>
       </c>
       <c r="AS37" t="n">
-        <v>1.93</v>
+        <v>2.6</v>
       </c>
       <c r="AT37" t="n">
-        <v>2.43</v>
+        <v>3.4</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AV37" t="n">
-        <v>2.85</v>
+        <v>2.1</v>
       </c>
       <c r="AW37" t="n">
-        <v>2.18</v>
+        <v>1.68</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.48</v>
+        <v>1.26</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.29</v>
+        <v>2.02</v>
       </c>
       <c r="BA37" t="n">
-        <v>3.7</v>
+        <v>2.02</v>
       </c>
       <c r="BB37" t="n">
         <v>0</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.97</v>
+        <v>2.12</v>
       </c>
       <c r="BD37" t="n">
         <v>0</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="BF37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,79 +7893,79 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="R38" t="n">
-        <v>2.6</v>
+        <v>2.87</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
@@ -7974,52 +7974,52 @@
         <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU38" t="n">
         <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,22 +8090,22 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R39" t="n">
-        <v>4.25</v>
+        <v>3.3</v>
       </c>
       <c r="S39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -8114,106 +8114,106 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN39" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AT39" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AU39" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AV39" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BA39" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BB39" t="n">
         <v>0</v>
       </c>
       <c r="BC39" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="BD39" t="n">
         <v>0</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BF39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.55</v>
+        <v>1.84</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="R40" t="n">
-        <v>6</v>
+        <v>4.14</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,22 +8484,22 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="R41" t="n">
-        <v>4.24</v>
+        <v>6</v>
       </c>
       <c r="S41" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -8508,106 +8508,106 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AT41" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AU41" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AV41" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AW41" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA41" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BB41" t="n">
         <v>0</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD41" t="n">
         <v>0</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BF41" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.16</v>
+        <v>1.88</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="R43" t="n">
-        <v>3.3</v>
+        <v>3.72</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,133 +9075,133 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R44" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S44" t="n">
-        <v>3.52</v>
+        <v>3.8</v>
       </c>
       <c r="T44" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="U44" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W44" t="n">
         <v>2.85</v>
       </c>
-      <c r="V44" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W44" t="n">
-        <v>2.95</v>
-      </c>
       <c r="X44" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Z44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI44" t="n">
         <v>6</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>5.4</v>
       </c>
       <c r="AJ44" t="n">
         <v>1.09</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="AL44" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AM44" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AN44" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.52</v>
+        <v>1.78</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.81</v>
+        <v>2.23</v>
       </c>
       <c r="AT44" t="n">
-        <v>2.23</v>
+        <v>2.9</v>
       </c>
       <c r="AU44" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AV44" t="n">
-        <v>3.1</v>
+        <v>2.43</v>
       </c>
       <c r="AW44" t="n">
-        <v>2.33</v>
+        <v>1.9</v>
       </c>
       <c r="AX44" t="n">
-        <v>1.87</v>
+        <v>1.56</v>
       </c>
       <c r="AY44" t="n">
-        <v>1.56</v>
+        <v>1.35</v>
       </c>
       <c r="AZ44" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="BA44" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC44" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="BD44" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,130 +9272,130 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3.4</v>
+        <v>1.95</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R45" t="n">
-        <v>2.17</v>
+        <v>3.9</v>
       </c>
       <c r="S45" t="n">
-        <v>3.8</v>
+        <v>2.48</v>
       </c>
       <c r="T45" t="n">
         <v>2.2</v>
       </c>
       <c r="U45" t="n">
-        <v>2.7</v>
+        <v>3.95</v>
       </c>
       <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH45" t="n">
         <v>1.33</v>
       </c>
-      <c r="W45" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="X45" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AI45" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AL45" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="AM45" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AN45" t="n">
-        <v>1.26</v>
+        <v>1.76</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="AS45" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="AT45" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="AU45" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="AV45" t="n">
-        <v>2.43</v>
+        <v>2.63</v>
       </c>
       <c r="AW45" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="AX45" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AY45" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AZ45" t="n">
-        <v>2.43</v>
+        <v>1.52</v>
       </c>
       <c r="BA45" t="n">
-        <v>1.65</v>
+        <v>2.88</v>
       </c>
       <c r="BB45" t="n">
         <v>0</v>
       </c>
       <c r="BC45" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="BD45" t="n">
         <v>0</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="BF45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,22 +9469,22 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="R46" t="n">
-        <v>3.54</v>
+        <v>4.24</v>
       </c>
       <c r="S46" t="n">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="T46" t="n">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="U46" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -9493,43 +9493,43 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="Z46" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AB46" t="n">
         <v>0</v>
       </c>
       <c r="AC46" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AJ46" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>1.16</v>
       </c>
       <c r="AK46" t="n">
         <v>1.55</v>
@@ -9538,61 +9538,61 @@
         <v>2.25</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AN46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC46" t="n">
         <v>1.79</v>
       </c>
-      <c r="AO46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP46" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ46" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX46" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AY46" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ46" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BA46" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BB46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC46" t="n">
-        <v>1.86</v>
-      </c>
       <c r="BD46" t="n">
         <v>0</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="BF46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,22 +9666,22 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.95</v>
+        <v>2.65</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="R47" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="S47" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
         <v>0</v>
@@ -9690,106 +9690,106 @@
         <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
         <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI47" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AM47" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN47" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS47" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AT47" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU47" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AV47" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW47" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX47" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AY47" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ47" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BA47" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BB47" t="n">
         <v>0</v>
       </c>
       <c r="BC47" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="BD47" t="n">
         <v>0</v>
       </c>
       <c r="BE47" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BF47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,40 +9863,40 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R48" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="S48" t="n">
-        <v>2.65</v>
+        <v>3.52</v>
       </c>
       <c r="T48" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="U48" t="n">
-        <v>3.5</v>
+        <v>2.85</v>
       </c>
       <c r="V48" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W48" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="X48" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Z48" t="n">
         <v>6</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AB48" t="n">
         <v>1</v>
@@ -9914,76 +9914,76 @@
         <v>1.89</v>
       </c>
       <c r="AG48" t="n">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AI48" t="n">
         <v>5.4</v>
       </c>
       <c r="AJ48" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AL48" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AM48" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AN48" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BA48" t="n">
         <v>1.63</v>
       </c>
-      <c r="AO48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AX48" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY48" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AZ48" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BA48" t="n">
-        <v>2.18</v>
-      </c>
       <c r="BB48" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BC48" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="BD48" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="BE48" t="n">
         <v>1.68</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,133 +10060,133 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R49" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="S49" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="T49" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="U49" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="V49" t="n">
         <v>1.38</v>
       </c>
       <c r="W49" t="n">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="X49" t="n">
         <v>2.88</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z49" t="n">
-        <v>6.25</v>
+        <v>6.95</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AD49" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="AG49" t="n">
-        <v>3.05</v>
+        <v>3.42</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AI49" t="n">
-        <v>6.4</v>
+        <v>6.75</v>
       </c>
       <c r="AJ49" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AK49" t="n">
         <v>1.8</v>
       </c>
       <c r="AL49" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AM49" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AN49" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="AS49" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AT49" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AU49" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AV49" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AW49" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="AX49" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AY49" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AZ49" t="n">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="BA49" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="BB49" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="BC49" t="n">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
       <c r="BD49" t="n">
-        <v>3.75</v>
+        <v>3.36</v>
       </c>
       <c r="BE49" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,130 +10257,130 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="R50" t="n">
-        <v>2.85</v>
+        <v>3.54</v>
       </c>
       <c r="S50" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="T50" t="n">
-        <v>2.17</v>
+        <v>2.35</v>
       </c>
       <c r="U50" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="V50" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AT50" t="n">
         <v>2.7</v>
       </c>
-      <c r="Y50" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN50" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AQ50" t="n">
+      <c r="AU50" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX50" t="n">
         <v>1.63</v>
       </c>
-      <c r="AR50" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AY50" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AZ50" t="n">
-        <v>2.02</v>
+        <v>1.7</v>
       </c>
       <c r="BA50" t="n">
-        <v>2.02</v>
+        <v>2.43</v>
       </c>
       <c r="BB50" t="n">
         <v>0</v>
       </c>
       <c r="BC50" t="n">
-        <v>2.12</v>
+        <v>1.86</v>
       </c>
       <c r="BD50" t="n">
         <v>0</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="BF50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,76 +10454,76 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="Q51" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R51" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S51" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U51" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD51" t="n">
         <v>3.3</v>
       </c>
-      <c r="R51" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S51" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T51" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U51" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="V51" t="n">
-        <v>0</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AE51" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="AG51" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AI51" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AL51" t="n">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="AM51" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AN51" t="n">
         <v>1.43</v>
@@ -10532,52 +10532,52 @@
         <v>0</v>
       </c>
       <c r="AP51" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AS51" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC51" t="n">
         <v>2.12</v>
       </c>
-      <c r="AT51" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="BA51" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BB51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC51" t="n">
-        <v>1.98</v>
-      </c>
       <c r="BD51" t="n">
         <v>0</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="BF51" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,22 +11045,22 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.88</v>
+        <v>2.6</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.74</v>
+        <v>3.3</v>
       </c>
       <c r="R54" t="n">
-        <v>3.72</v>
+        <v>2.55</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V54" t="n">
         <v>0</v>
@@ -11069,10 +11069,10 @@
         <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -11084,40 +11084,40 @@
         <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI54" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK54" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL54" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AM54" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN54" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AO54" t="n">
         <v>0</v>
@@ -11126,49 +11126,49 @@
         <v>0</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR54" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS54" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AT54" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU54" t="n">
         <v>0</v>
       </c>
       <c r="AV54" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW54" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX54" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY54" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ54" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="BA54" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BB54" t="n">
         <v>0</v>
       </c>
       <c r="BC54" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD54" t="n">
         <v>0</v>
       </c>
       <c r="BE54" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,61 +11242,61 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="R55" t="n">
-        <v>2.87</v>
+        <v>4.5</v>
       </c>
       <c r="S55" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="T55" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="U55" t="n">
-        <v>3.46</v>
+        <v>4.4</v>
       </c>
       <c r="V55" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="Y55" t="n">
         <v>1.45</v>
       </c>
       <c r="Z55" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AD55" t="n">
         <v>3.7</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AG55" t="n">
         <v>2.85</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AI55" t="n">
         <v>5.1</v>
@@ -11305,70 +11305,70 @@
         <v>1.12</v>
       </c>
       <c r="AK55" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR55" t="n">
         <v>1.58</v>
       </c>
-      <c r="AL55" t="n">
+      <c r="AS55" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AW55" t="n">
         <v>2.18</v>
       </c>
-      <c r="AM55" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN55" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AO55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>2.08</v>
-      </c>
       <c r="AX55" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AY55" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AZ55" t="n">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="BA55" t="n">
-        <v>2.55</v>
+        <v>3.7</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BC55" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="BD55" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE55" t="n">
         <v>1.72</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,133 +11439,133 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.47</v>
+        <v>2.07</v>
       </c>
       <c r="Q56" t="n">
-        <v>5.5</v>
+        <v>3.9</v>
       </c>
       <c r="R56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S56" t="n">
-        <v>1.93</v>
+        <v>2.6</v>
       </c>
       <c r="T56" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="U56" t="n">
-        <v>4.24</v>
+        <v>3.1</v>
       </c>
       <c r="V56" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W56" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="X56" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="Z56" t="n">
-        <v>4.55</v>
+        <v>4.33</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AB56" t="n">
         <v>1.01</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AD56" t="n">
-        <v>5.1</v>
+        <v>5.45</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AF56" t="n">
-        <v>2.55</v>
+        <v>2.78</v>
       </c>
       <c r="AG56" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AI56" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="AJ56" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK56" t="n">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="AL56" t="n">
-        <v>2.21</v>
+        <v>2.81</v>
       </c>
       <c r="AM56" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AN56" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="AO56" t="n">
         <v>0</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.27</v>
+        <v>1.58</v>
       </c>
       <c r="AS56" t="n">
-        <v>1.44</v>
+        <v>1.93</v>
       </c>
       <c r="AT56" t="n">
-        <v>1.68</v>
+        <v>2.43</v>
       </c>
       <c r="AU56" t="n">
-        <v>6.5</v>
+        <v>3.95</v>
       </c>
       <c r="AV56" t="n">
-        <v>4.6</v>
+        <v>2.88</v>
       </c>
       <c r="AW56" t="n">
-        <v>3.35</v>
+        <v>2.2</v>
       </c>
       <c r="AX56" t="n">
-        <v>2.55</v>
+        <v>1.76</v>
       </c>
       <c r="AY56" t="n">
-        <v>2.02</v>
+        <v>1.48</v>
       </c>
       <c r="AZ56" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BB56" t="n">
         <v>1.12</v>
       </c>
-      <c r="BA56" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="BB56" t="n">
-        <v>1.15</v>
-      </c>
       <c r="BC56" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="BD56" t="n">
-        <v>5.05</v>
+        <v>5.25</v>
       </c>
       <c r="BE56" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="BF56" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,133 +11636,133 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="R57" t="n">
-        <v>3</v>
+        <v>3.19</v>
       </c>
       <c r="S57" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U57" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V57" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI57" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AJ57" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK57" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL57" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AM57" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN57" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AO57" t="n">
         <v>0</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AR57" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AS57" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AT57" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AU57" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AV57" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AW57" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AX57" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AY57" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AZ57" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BA57" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BB57" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC57" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BD57" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="BE57" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BF57" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BG57" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,133 +12030,133 @@
         </is>
       </c>
       <c r="P59" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R59" t="n">
+        <v>5</v>
+      </c>
+      <c r="S59" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U59" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W59" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="X59" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q59" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R59" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" t="n">
-        <v>0</v>
-      </c>
-      <c r="W59" t="n">
-        <v>0</v>
-      </c>
-      <c r="X59" t="n">
-        <v>0</v>
-      </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG59" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH59" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AI59" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK59" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL59" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AM59" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN59" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AO59" t="n">
         <v>0</v>
       </c>
       <c r="AP59" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AQ59" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AR59" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AS59" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AT59" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AU59" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AV59" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AW59" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AX59" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AY59" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AZ59" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BA59" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="BB59" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC59" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BD59" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="BE59" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF59" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG59" t="n">
         <v>0</v>

--- a/jogos_2026-03-17.xlsx
+++ b/jogos_2026-03-17.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="R7" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="S7" t="n">
         <v>2.15</v>
@@ -1849,10 +1849,10 @@
         <v>1.08</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AM7" t="n">
         <v>1.24</v>
@@ -1983,16 +1983,16 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.5</v>
+        <v>6.25</v>
       </c>
       <c r="R8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S8" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="T8" t="n">
         <v>2.85</v>
@@ -2034,7 +2034,7 @@
         <v>2.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AH8" t="n">
         <v>1.76</v>
@@ -2046,7 +2046,7 @@
         <v>1.27</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AL8" t="n">
         <v>1.83</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,143 +3358,143 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="R15" t="n">
-        <v>4.37</v>
+        <v>4.58</v>
       </c>
       <c r="S15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AV15" t="n">
         <v>2.16</v>
       </c>
-      <c r="T15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W15" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR15" t="n">
+      <c r="AW15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
         <v>1.62</v>
       </c>
-      <c r="AS15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.9</v>
-      </c>
       <c r="BF15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BH15" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="BI15" s="3" t="n">
         <v>46098.625</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,22 +3756,22 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3780,10 +3780,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -3795,91 +3795,91 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
         <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
         <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,143 +3949,143 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BH18" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="BI18" s="3" t="n">
         <v>46098.625</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4231,10 +4231,10 @@
         <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
         <v>0</v>
@@ -4246,10 +4246,10 @@
         <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4625,10 +4625,10 @@
         <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AS21" t="n">
         <v>0</v>
@@ -4640,10 +4640,10 @@
         <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX21" t="n">
         <v>0</v>
@@ -4658,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.02</v>
+        <v>1.91</v>
       </c>
       <c r="Q24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W24" t="n">
+        <v>4</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI24" t="n">
         <v>3.2</v>
       </c>
-      <c r="R24" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>6.5</v>
-      </c>
       <c r="AJ24" t="n">
-        <v>1.07</v>
+        <v>1.29</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AL24" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AX24" t="n">
         <v>1.89</v>
       </c>
-      <c r="AM24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AY24" t="n">
-        <v>1.26</v>
+        <v>1.57</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2.18</v>
+        <v>1.57</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.28</v>
+        <v>1.58</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.55</v>
+        <v>2.23</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q25" t="n">
         <v>4.1</v>
       </c>
-      <c r="Q25" t="n">
-        <v>3.35</v>
-      </c>
       <c r="R25" t="n">
-        <v>1.89</v>
+        <v>4.3</v>
       </c>
       <c r="S25" t="n">
-        <v>4.5</v>
+        <v>2.16</v>
       </c>
       <c r="T25" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="U25" t="n">
-        <v>2.43</v>
+        <v>4.22</v>
       </c>
       <c r="V25" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="W25" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AL25" t="n">
         <v>2.63</v>
       </c>
-      <c r="X25" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="n">
+      <c r="AM25" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BF25" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>3</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,34 +5529,34 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.26</v>
+        <v>1.33</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="R26" t="n">
-        <v>3.11</v>
+        <v>8.4</v>
       </c>
       <c r="S26" t="n">
-        <v>2.75</v>
+        <v>1.7</v>
       </c>
       <c r="T26" t="n">
-        <v>2.14</v>
+        <v>2.6</v>
       </c>
       <c r="U26" t="n">
-        <v>3.55</v>
+        <v>7</v>
       </c>
       <c r="V26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
@@ -5568,91 +5568,91 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.15</v>
+        <v>4.35</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.96</v>
+        <v>1.57</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.73</v>
+        <v>2.23</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="AI26" t="n">
-        <v>6.25</v>
+        <v>4.25</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AM26" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
         <v>1.29</v>
       </c>
-      <c r="AN26" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ26" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.76</v>
+        <v>1.21</v>
       </c>
       <c r="BA26" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="BB26" t="n">
         <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="BD26" t="n">
         <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.58</v>
+        <v>1.88</v>
       </c>
       <c r="BF26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5807,49 +5807,49 @@
         <v>0</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AU27" t="n">
         <v>0</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BB27" t="n">
         <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD27" t="n">
         <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,79 +5923,79 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.62</v>
+        <v>2.26</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="R28" t="n">
-        <v>4.3</v>
+        <v>3.11</v>
       </c>
       <c r="S28" t="n">
-        <v>2.16</v>
+        <v>2.75</v>
       </c>
       <c r="T28" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="U28" t="n">
-        <v>4.22</v>
+        <v>3.55</v>
       </c>
       <c r="V28" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="W28" t="n">
-        <v>3.82</v>
+        <v>2.85</v>
       </c>
       <c r="X28" t="n">
-        <v>2.06</v>
+        <v>2.75</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ28" t="n">
         <v>1.08</v>
       </c>
-      <c r="AD28" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AK28" t="n">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="AL28" t="n">
-        <v>2.63</v>
+        <v>1.94</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AN28" t="n">
-        <v>2.07</v>
+        <v>1.56</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6004,52 +6004,52 @@
         <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.36</v>
+        <v>2.75</v>
       </c>
       <c r="AU28" t="n">
         <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>3.14</v>
+        <v>2.55</v>
       </c>
       <c r="AW28" t="n">
-        <v>2.29</v>
+        <v>1.96</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="BA28" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.61</v>
+        <v>2.2</v>
       </c>
       <c r="BD28" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>2.15</v>
+        <v>1.58</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BD29" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,130 +6514,130 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.64</v>
+        <v>4.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="R31" t="n">
-        <v>4.49</v>
+        <v>1.89</v>
       </c>
       <c r="S31" t="n">
-        <v>2.14</v>
+        <v>4.5</v>
       </c>
       <c r="T31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W31" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="X31" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU31" t="n">
         <v>2.55</v>
       </c>
-      <c r="U31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W31" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AE31" t="n">
+      <c r="AV31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE31" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>1.95</v>
       </c>
       <c r="BF31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,130 +6711,130 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.33</v>
+        <v>3.02</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.9</v>
+        <v>3.2</v>
       </c>
       <c r="R32" t="n">
-        <v>8.4</v>
+        <v>2.31</v>
       </c>
       <c r="S32" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="T32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="X32" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AS32" t="n">
         <v>2.6</v>
       </c>
-      <c r="U32" t="n">
-        <v>7</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y32" t="n">
+      <c r="AT32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE32" t="n">
         <v>1.55</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>1.88</v>
       </c>
       <c r="BF32" t="n">
         <v>0</v>
@@ -6911,10 +6911,10 @@
         <v>4</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R33" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="S33" t="n">
         <v>4.2</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,22 +7105,22 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.15</v>
+        <v>2.66</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R34" t="n">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="S34" t="n">
-        <v>2.8</v>
+        <v>3.16</v>
       </c>
       <c r="T34" t="n">
         <v>2.08</v>
       </c>
       <c r="U34" t="n">
-        <v>3.9</v>
+        <v>3.24</v>
       </c>
       <c r="V34" t="n">
         <v>1.38</v>
@@ -7129,109 +7129,109 @@
         <v>2.81</v>
       </c>
       <c r="X34" t="n">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="Z34" t="n">
-        <v>6.25</v>
+        <v>6.65</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC34" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD34" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AQ34" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AR34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX34" t="n">
         <v>1.64</v>
       </c>
-      <c r="AS34" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AW34" t="n">
+      <c r="AY34" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC34" t="n">
         <v>2.08</v>
       </c>
-      <c r="AX34" t="n">
+      <c r="BD34" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="BE34" t="n">
         <v>1.7</v>
       </c>
-      <c r="AY34" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>1.66</v>
-      </c>
       <c r="BF34" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,130 +7302,130 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="R35" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="S35" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="T35" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="U35" t="n">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="V35" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W35" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="X35" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="Z35" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AB35" t="n">
         <v>1</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.99</v>
+        <v>2.85</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AI35" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AL35" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AW35" t="n">
         <v>2.08</v>
       </c>
-      <c r="AM35" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AX35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AZ35" t="n">
         <v>1.56</v>
       </c>
-      <c r="AY35" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>1.88</v>
-      </c>
       <c r="BA35" t="n">
-        <v>2.18</v>
+        <v>2.55</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="BF35" t="n">
         <v>1.16</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,22 +7499,22 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.85</v>
+        <v>2.65</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="R36" t="n">
-        <v>4.25</v>
+        <v>2.6</v>
       </c>
       <c r="S36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -7523,106 +7523,106 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AT36" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BA36" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BB36" t="n">
         <v>0</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="BD36" t="n">
         <v>0</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BF36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,130 +7696,130 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="R37" t="n">
-        <v>2.85</v>
+        <v>3.8</v>
       </c>
       <c r="S37" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT37" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="BA37" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="BB37" t="n">
         <v>0</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="BD37" t="n">
         <v>0</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,79 +7893,79 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R38" t="n">
-        <v>2.87</v>
+        <v>2.15</v>
       </c>
       <c r="S38" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.82</v>
+        <v>2.6</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.96</v>
+        <v>1.47</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
@@ -7974,52 +7974,52 @@
         <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="n">
         <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BA38" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD38" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="R39" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8287,10 +8287,10 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R40" t="n">
         <v>4.14</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8487,10 +8487,10 @@
         <v>1.55</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="R41" t="n">
-        <v>6</v>
+        <v>5.73</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.66</v>
+        <v>1.6</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.32</v>
+        <v>4.2</v>
       </c>
       <c r="R42" t="n">
-        <v>2.55</v>
+        <v>5.4</v>
       </c>
       <c r="S42" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AG42" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AS42" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AT42" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU42" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BA42" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC42" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BD42" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,79 +8878,79 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.88</v>
+        <v>3.9</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="R43" t="n">
-        <v>3.72</v>
+        <v>1.95</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
@@ -8959,52 +8959,52 @@
         <v>0</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR43" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS43" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AU43" t="n">
         <v>0</v>
       </c>
       <c r="AV43" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AX43" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AY43" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BA43" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BB43" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC43" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BD43" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF43" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,130 +9075,130 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3.4</v>
+        <v>1.85</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="R44" t="n">
-        <v>2.17</v>
+        <v>3.54</v>
       </c>
       <c r="S44" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U44" t="n">
         <v>3.8</v>
       </c>
-      <c r="T44" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AT44" t="n">
         <v>2.7</v>
       </c>
-      <c r="V44" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W44" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="X44" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AO44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AQ44" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AT44" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AU44" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="AV44" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BA44" t="n">
         <v>2.43</v>
       </c>
-      <c r="AW44" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AZ44" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BA44" t="n">
-        <v>1.65</v>
-      </c>
       <c r="BB44" t="n">
         <v>0</v>
       </c>
       <c r="BC44" t="n">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="BD44" t="n">
         <v>0</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="BF44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,133 +9272,133 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.95</v>
+        <v>2.37</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="R45" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="S45" t="n">
-        <v>2.48</v>
+        <v>2.85</v>
       </c>
       <c r="T45" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W45" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="X45" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BA45" t="n">
         <v>2.2</v>
       </c>
-      <c r="U45" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC45" t="n">
+      <c r="BB45" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD45" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AO45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP45" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AQ45" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AT45" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AU45" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV45" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AW45" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AX45" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AY45" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AZ45" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BA45" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BB45" t="n">
-        <v>0</v>
-      </c>
       <c r="BC45" t="n">
-        <v>2.04</v>
+        <v>2.27</v>
       </c>
       <c r="BD45" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="BF45" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,133 +9469,133 @@
         </is>
       </c>
       <c r="P46" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R46" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W46" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="X46" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE46" t="n">
         <v>1.68</v>
       </c>
-      <c r="Q46" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R46" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="S46" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="U46" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC46" t="n">
+      <c r="BF46" t="n">
         <v>1.16</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP46" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AQ46" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AX46" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AY46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AZ46" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BA46" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BB46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC46" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BD46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE46" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BF46" t="n">
-        <v>0</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,34 +9666,34 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.65</v>
+        <v>3.65</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="R47" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z47" t="n">
         <v>0</v>
@@ -9705,91 +9705,91 @@
         <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN47" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AR47" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AS47" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AU47" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AV47" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AW47" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX47" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AY47" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BA47" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BB47" t="n">
         <v>0</v>
       </c>
       <c r="BC47" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD47" t="n">
         <v>0</v>
       </c>
       <c r="BE47" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BF47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,133 +9863,133 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.9</v>
+        <v>1.68</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R48" t="n">
-        <v>2.3</v>
+        <v>4.24</v>
       </c>
       <c r="S48" t="n">
-        <v>3.52</v>
+        <v>2.14</v>
       </c>
       <c r="T48" t="n">
-        <v>2.15</v>
+        <v>2.43</v>
       </c>
       <c r="U48" t="n">
-        <v>2.85</v>
+        <v>4.3</v>
       </c>
       <c r="V48" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="Z48" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AB48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AD48" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AE48" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC48" t="n">
         <v>1.79</v>
       </c>
-      <c r="AF48" t="n">
+      <c r="BD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE48" t="n">
         <v>1.89</v>
       </c>
-      <c r="AG48" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AX48" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AY48" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AZ48" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BA48" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BB48" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC48" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BD48" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE48" t="n">
-        <v>1.68</v>
-      </c>
       <c r="BF48" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,133 +10060,133 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="Q49" t="n">
         <v>3.2</v>
       </c>
       <c r="R49" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="S49" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="T49" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="U49" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="V49" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W49" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X49" t="n">
         <v>2.7</v>
       </c>
-      <c r="X49" t="n">
-        <v>2.88</v>
-      </c>
       <c r="Y49" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z49" t="n">
-        <v>6.95</v>
+        <v>6.25</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AD49" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AE49" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="AF49" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK49" t="n">
         <v>1.68</v>
       </c>
-      <c r="AG49" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AL49" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AM49" t="n">
         <v>1.28</v>
       </c>
       <c r="AN49" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
       </c>
       <c r="AP49" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ49" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX49" t="n">
         <v>1.43</v>
       </c>
-      <c r="AR49" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV49" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW49" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AX49" t="n">
+      <c r="AY49" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE49" t="n">
         <v>1.63</v>
       </c>
-      <c r="AY49" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AZ49" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BA49" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BB49" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC49" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="BD49" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="BE49" t="n">
-        <v>1.56</v>
-      </c>
       <c r="BF49" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,22 +10257,22 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="R50" t="n">
-        <v>3.54</v>
+        <v>3.75</v>
       </c>
       <c r="S50" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="T50" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="U50" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="V50" t="n">
         <v>0</v>
@@ -10281,106 +10281,106 @@
         <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="Y50" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ50" t="n">
         <v>1.52</v>
       </c>
-      <c r="Z50" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN50" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AY50" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ50" t="n">
-        <v>1.7</v>
-      </c>
       <c r="BA50" t="n">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="BB50" t="n">
         <v>0</v>
       </c>
       <c r="BC50" t="n">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="BD50" t="n">
         <v>0</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="BF50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,133 +10454,133 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.65</v>
+        <v>2.08</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="R51" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="S51" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="T51" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="U51" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="X51" t="n">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AD51" t="n">
         <v>3.3</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AF51" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK51" t="n">
         <v>1.8</v>
       </c>
-      <c r="AG51" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH51" t="n">
+      <c r="AL51" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AM51" t="n">
         <v>1.29</v>
       </c>
-      <c r="AI51" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK51" t="n">
+      <c r="AN51" t="n">
         <v>1.68</v>
       </c>
-      <c r="AL51" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AO51" t="n">
         <v>0</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="AS51" t="n">
-        <v>2.43</v>
+        <v>2</v>
       </c>
       <c r="AT51" t="n">
-        <v>3.15</v>
+        <v>2.55</v>
       </c>
       <c r="AU51" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="AV51" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AW51" t="n">
-        <v>1.78</v>
+        <v>2.08</v>
       </c>
       <c r="AX51" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AY51" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AZ51" t="n">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="BA51" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="BB51" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC51" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="BD51" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="BF51" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,22 +10651,22 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>3.35</v>
+        <v>2.6</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R52" t="n">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V52" t="n">
         <v>0</v>
@@ -10675,10 +10675,10 @@
         <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z52" t="n">
         <v>0</v>
@@ -10690,40 +10690,40 @@
         <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI52" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK52" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL52" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AM52" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN52" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AO52" t="n">
         <v>0</v>
@@ -10732,49 +10732,49 @@
         <v>0</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR52" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS52" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AT52" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU52" t="n">
         <v>0</v>
       </c>
       <c r="AV52" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW52" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX52" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY52" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ52" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="BA52" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BB52" t="n">
         <v>0</v>
       </c>
       <c r="BC52" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD52" t="n">
         <v>0</v>
       </c>
       <c r="BE52" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,22 +10848,22 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="Q53" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="R53" t="n">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V53" t="n">
         <v>0</v>
@@ -10872,106 +10872,106 @@
         <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB53" t="n">
         <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI53" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL53" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AM53" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN53" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR53" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS53" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AT53" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AU53" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AV53" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW53" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AX53" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AY53" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AZ53" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BA53" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BB53" t="n">
         <v>0</v>
       </c>
       <c r="BC53" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BD53" t="n">
         <v>0</v>
       </c>
       <c r="BE53" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,76 +11045,76 @@
         </is>
       </c>
       <c r="P54" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R54" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="S54" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U54" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD54" t="n">
         <v>3.3</v>
       </c>
-      <c r="R54" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S54" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T54" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U54" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="V54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X54" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AE54" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="AG54" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AI54" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="AJ54" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AL54" t="n">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="AM54" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AN54" t="n">
         <v>1.43</v>
@@ -11123,52 +11123,52 @@
         <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AS54" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC54" t="n">
         <v>2.12</v>
       </c>
-      <c r="AT54" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV54" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AW54" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AX54" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY54" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ54" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="BA54" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BB54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC54" t="n">
-        <v>1.98</v>
-      </c>
       <c r="BD54" t="n">
         <v>0</v>
       </c>
       <c r="BE54" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="BF54" t="n">
         <v>0</v>
@@ -11242,10 +11242,10 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="R55" t="n">
         <v>4.5</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,133 +11636,133 @@
         </is>
       </c>
       <c r="P57" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R57" t="n">
+        <v>5</v>
+      </c>
+      <c r="S57" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U57" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W57" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="X57" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q57" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R57" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" t="n">
-        <v>0</v>
-      </c>
-      <c r="V57" t="n">
-        <v>0</v>
-      </c>
-      <c r="W57" t="n">
-        <v>0</v>
-      </c>
-      <c r="X57" t="n">
-        <v>0</v>
-      </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AI57" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK57" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL57" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AM57" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN57" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AO57" t="n">
         <v>0</v>
       </c>
       <c r="AP57" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AR57" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AS57" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AT57" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AU57" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AV57" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AW57" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AX57" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AY57" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AZ57" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BA57" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="BB57" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC57" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BD57" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="BE57" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF57" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,133 +11833,133 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q58" t="n">
-        <v>5.5</v>
+        <v>3.55</v>
       </c>
       <c r="R58" t="n">
-        <v>8.9</v>
+        <v>3.19</v>
       </c>
       <c r="S58" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U58" t="n">
-        <v>8.779999999999999</v>
+        <v>0</v>
       </c>
       <c r="V58" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="X58" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AI58" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AJ58" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK58" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AL58" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AM58" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AN58" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AO58" t="n">
         <v>0</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AR58" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AS58" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AT58" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AU58" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AV58" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AW58" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AX58" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AY58" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AZ58" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BA58" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="BB58" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC58" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BD58" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BE58" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BF58" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,133 +12030,133 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="Q59" t="n">
         <v>5.5</v>
       </c>
       <c r="R59" t="n">
-        <v>5</v>
+        <v>8.9</v>
       </c>
       <c r="S59" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="T59" t="n">
-        <v>2.42</v>
+        <v>2.77</v>
       </c>
       <c r="U59" t="n">
-        <v>4.24</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="V59" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W59" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X59" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK59" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP59" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AQ59" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AR59" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AT59" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AU59" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV59" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AW59" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AX59" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AY59" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AZ59" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BA59" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="BB59" t="n">
         <v>1.17</v>
       </c>
-      <c r="W59" t="n">
+      <c r="BC59" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BD59" t="n">
         <v>4.75</v>
       </c>
-      <c r="X59" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AE59" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AG59" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH59" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AI59" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AJ59" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK59" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AL59" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AM59" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN59" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AO59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP59" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AQ59" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AR59" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AS59" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AT59" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AU59" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AV59" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW59" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AX59" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AY59" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AZ59" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BA59" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="BB59" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BC59" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BD59" t="n">
-        <v>5.05</v>
-      </c>
       <c r="BE59" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="BF59" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="BG59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G65" t="n">

--- a/jogos_2026-03-17.xlsx
+++ b/jogos_2026-03-17.xlsx
@@ -801,22 +801,22 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="R2" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="S2" t="n">
         <v>2.79</v>
       </c>
       <c r="T2" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="U2" t="n">
-        <v>3.58</v>
+        <v>3.17</v>
       </c>
       <c r="V2" t="n">
         <v>1.33</v>
@@ -846,10 +846,10 @@
         <v>3.8</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="AG2" t="n">
         <v>2.78</v>
@@ -864,25 +864,25 @@
         <v>1.13</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AL2" t="n">
         <v>2.23</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR2" t="n">
         <v>1.73</v>
@@ -891,22 +891,22 @@
         <v>2.14</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.15</v>
+        <v>4.3</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AW2" t="n">
         <v>1.96</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AZ2" t="n">
         <v>2.09</v>
@@ -915,7 +915,7 @@
         <v>1.96</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BC2" t="n">
         <v>1.95</v>
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.78</v>
+        <v>7.3</v>
       </c>
       <c r="R8" t="n">
-        <v>11.95</v>
+        <v>11</v>
       </c>
       <c r="S8" t="n">
         <v>1.56</v>
@@ -2013,7 +2013,7 @@
         <v>1.67</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA8" t="n">
         <v>1.14</v>
@@ -2097,13 +2097,13 @@
         <v>7.7</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="BC8" t="n">
         <v>1.73</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.8</v>
+        <v>5.75</v>
       </c>
       <c r="BE8" t="n">
         <v>2</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,139 +3362,139 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.82</v>
+        <v>3.7</v>
       </c>
       <c r="R15" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="S15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T15" t="n">
         <v>2.14</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS15" t="n">
         <v>2.48</v>
       </c>
-      <c r="U15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W15" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA15" t="n">
+      <c r="AT15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BF15" t="n">
         <v>1.14</v>
       </c>
-      <c r="AB15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>1.22</v>
-      </c>
       <c r="BG15" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BH15" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="BI15" s="3" t="n">
         <v>46098.625</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,139 +3559,139 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BH16" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="BI16" s="3" t="n">
         <v>46098.625</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4231,10 +4231,10 @@
         <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AS19" t="n">
         <v>0</v>
@@ -4246,10 +4246,10 @@
         <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4356,70 +4356,70 @@
         <v>4.13</v>
       </c>
       <c r="S20" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="T20" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="U20" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="V20" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W20" t="n">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="X20" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="AA20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC20" t="n">
         <v>1.13</v>
       </c>
-      <c r="AB20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AD20" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH20" t="n">
         <v>1.65</v>
       </c>
       <c r="AI20" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AN20" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4455,25 +4455,25 @@
         <v>1.32</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.67</v>
+        <v>2.42</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="